--- a/outputs/mfcc_features.xlsx
+++ b/outputs/mfcc_features.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:AC80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1148,1425 +1148,6935 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>person 2</t>
+          <t>person 12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Harshita_1.ogg</t>
+          <t>aman_1.ogg</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dataset\person 2\Harshita_1.ogg</t>
+          <t>dataset\person 12\aman_1.ogg</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-286.7710876464844</v>
+        <v>-634.4279174804688</v>
       </c>
       <c r="E8" t="n">
-        <v>145.6819763183594</v>
+        <v>68.22845458984375</v>
       </c>
       <c r="F8" t="n">
-        <v>36.14165115356445</v>
+        <v>32.48543930053711</v>
       </c>
       <c r="G8" t="n">
-        <v>19.86843681335449</v>
+        <v>20.69969940185547</v>
       </c>
       <c r="H8" t="n">
-        <v>-16.67756271362305</v>
+        <v>15.78039169311523</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.458644866943359</v>
+        <v>8.514751434326172</v>
       </c>
       <c r="J8" t="n">
-        <v>3.599449872970581</v>
+        <v>1.261267781257629</v>
       </c>
       <c r="K8" t="n">
-        <v>-7.693424224853516</v>
+        <v>-4.084224700927734</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.980954647064209</v>
+        <v>-3.059499025344849</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4789998531341553</v>
+        <v>3.889192581176758</v>
       </c>
       <c r="N8" t="n">
-        <v>-6.25227689743042</v>
+        <v>-1.256675362586975</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.499890089035034</v>
+        <v>-1.609464406967163</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.321202993392944</v>
+        <v>0.01789753139019012</v>
       </c>
       <c r="Q8" t="n">
-        <v>65.44059753417969</v>
+        <v>104.0619430541992</v>
       </c>
       <c r="R8" t="n">
-        <v>41.9994010925293</v>
+        <v>61.73273849487305</v>
       </c>
       <c r="S8" t="n">
-        <v>27.22202301025391</v>
+        <v>22.61662864685059</v>
       </c>
       <c r="T8" t="n">
-        <v>22.62238502502441</v>
+        <v>22.95244407653809</v>
       </c>
       <c r="U8" t="n">
-        <v>16.1590576171875</v>
+        <v>14.98680114746094</v>
       </c>
       <c r="V8" t="n">
-        <v>13.40995788574219</v>
+        <v>14.82222270965576</v>
       </c>
       <c r="W8" t="n">
-        <v>9.408201217651367</v>
+        <v>16.00283622741699</v>
       </c>
       <c r="X8" t="n">
-        <v>13.32199478149414</v>
+        <v>17.59932899475098</v>
       </c>
       <c r="Y8" t="n">
-        <v>10.54885101318359</v>
+        <v>15.51236534118652</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.566182136535645</v>
+        <v>9.456596374511719</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.690876960754395</v>
+        <v>11.0094108581543</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.26371955871582</v>
+        <v>7.047792434692383</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.744489192962646</v>
+        <v>5.562691688537598</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>person 2</t>
+          <t>person 12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Harshita_2.ogg</t>
+          <t>aman_3.ogg</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dataset\person 2\Harshita_2.ogg</t>
+          <t>dataset\person 12\aman_3.ogg</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-285.5520935058594</v>
+        <v>-636.7947998046875</v>
       </c>
       <c r="E9" t="n">
-        <v>146.4192199707031</v>
+        <v>61.81012725830078</v>
       </c>
       <c r="F9" t="n">
-        <v>31.81262016296387</v>
+        <v>26.98558044433594</v>
       </c>
       <c r="G9" t="n">
-        <v>19.22633743286133</v>
+        <v>33.92687225341797</v>
       </c>
       <c r="H9" t="n">
-        <v>-12.10067462921143</v>
+        <v>12.87245655059814</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.464438676834106</v>
+        <v>8.657885551452637</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2841993570327759</v>
+        <v>2.995275497436523</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.251331329345703</v>
+        <v>-5.445910930633545</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.298632860183716</v>
+        <v>0.2679830193519592</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6891754865646362</v>
+        <v>2.399663209915161</v>
       </c>
       <c r="N9" t="n">
-        <v>-9.162246704101562</v>
+        <v>-2.833395957946777</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03717708215117455</v>
+        <v>-2.130322217941284</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.480612277984619</v>
+        <v>-1.965862274169922</v>
       </c>
       <c r="Q9" t="n">
-        <v>64.51747131347656</v>
+        <v>120.0331344604492</v>
       </c>
       <c r="R9" t="n">
-        <v>45.21198654174805</v>
+        <v>59.08588790893555</v>
       </c>
       <c r="S9" t="n">
-        <v>28.2469482421875</v>
+        <v>28.40224075317383</v>
       </c>
       <c r="T9" t="n">
-        <v>22.09764671325684</v>
+        <v>31.61037445068359</v>
       </c>
       <c r="U9" t="n">
-        <v>15.96239948272705</v>
+        <v>16.20474243164062</v>
       </c>
       <c r="V9" t="n">
-        <v>13.65683841705322</v>
+        <v>20.9394416809082</v>
       </c>
       <c r="W9" t="n">
-        <v>9.648412704467773</v>
+        <v>15.96241283416748</v>
       </c>
       <c r="X9" t="n">
-        <v>14.66029357910156</v>
+        <v>18.86599731445312</v>
       </c>
       <c r="Y9" t="n">
-        <v>11.09800815582275</v>
+        <v>16.19884872436523</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.877726554870605</v>
+        <v>10.78779602050781</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.673047065734863</v>
+        <v>10.18557357788086</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.800985336303711</v>
+        <v>8.005271911621094</v>
       </c>
       <c r="AC9" t="n">
-        <v>6.93620777130127</v>
+        <v>7.674311637878418</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>person 3</t>
+          <t>person 12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kakul_1.ogg</t>
+          <t>aman_4.ogg</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dataset\person 3\Kakul_1.ogg</t>
+          <t>dataset\person 12\aman_4.ogg</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-190.283447265625</v>
+        <v>-425.4598999023438</v>
       </c>
       <c r="E10" t="n">
-        <v>133.6089477539062</v>
+        <v>111.4725036621094</v>
       </c>
       <c r="F10" t="n">
-        <v>1.115150809288025</v>
+        <v>37.44164276123047</v>
       </c>
       <c r="G10" t="n">
-        <v>23.2911205291748</v>
+        <v>27.32890319824219</v>
       </c>
       <c r="H10" t="n">
-        <v>-24.16946411132812</v>
+        <v>11.45980930328369</v>
       </c>
       <c r="I10" t="n">
-        <v>-7.406147956848145</v>
+        <v>-4.460370540618896</v>
       </c>
       <c r="J10" t="n">
-        <v>10.43996715545654</v>
+        <v>-7.79077672958374</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.800053119659424</v>
+        <v>-1.026360154151917</v>
       </c>
       <c r="L10" t="n">
-        <v>-7.63574743270874</v>
+        <v>-16.2560977935791</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.589412689208984</v>
+        <v>1.288555502891541</v>
       </c>
       <c r="N10" t="n">
-        <v>-9.197992324829102</v>
+        <v>-6.607500076293945</v>
       </c>
       <c r="O10" t="n">
-        <v>-8.793667793273926</v>
+        <v>-5.389003276824951</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.535579681396484</v>
+        <v>-5.544022560119629</v>
       </c>
       <c r="Q10" t="n">
-        <v>69.12535095214844</v>
+        <v>97.00936889648438</v>
       </c>
       <c r="R10" t="n">
-        <v>38.38052368164062</v>
+        <v>56.1270866394043</v>
       </c>
       <c r="S10" t="n">
-        <v>37.80652236938477</v>
+        <v>31.28457260131836</v>
       </c>
       <c r="T10" t="n">
-        <v>28.71722984313965</v>
+        <v>34.26152801513672</v>
       </c>
       <c r="U10" t="n">
-        <v>29.38401985168457</v>
+        <v>19.8060474395752</v>
       </c>
       <c r="V10" t="n">
-        <v>14.92785263061523</v>
+        <v>24.40964126586914</v>
       </c>
       <c r="W10" t="n">
-        <v>14.13958549499512</v>
+        <v>18.08007049560547</v>
       </c>
       <c r="X10" t="n">
-        <v>13.47562980651855</v>
+        <v>14.94317150115967</v>
       </c>
       <c r="Y10" t="n">
-        <v>11.11625480651855</v>
+        <v>18.20082855224609</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.429997444152832</v>
+        <v>13.47128200531006</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.36452198028564</v>
+        <v>9.745951652526855</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.37071514129639</v>
+        <v>8.741715431213379</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.672822952270508</v>
+        <v>9.291328430175781</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>person 3</t>
+          <t>person 13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kakul_2.ogg</t>
+          <t>roshan_1.ogg</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dataset\person 3\Kakul_2.ogg</t>
+          <t>dataset\person 13\roshan_1.ogg</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-196.8373107910156</v>
+        <v>-329.6038818359375</v>
       </c>
       <c r="E11" t="n">
-        <v>137.0163269042969</v>
+        <v>137.8912963867188</v>
       </c>
       <c r="F11" t="n">
-        <v>1.076949834823608</v>
+        <v>-4.476982116699219</v>
       </c>
       <c r="G11" t="n">
-        <v>20.15438652038574</v>
+        <v>20.20308494567871</v>
       </c>
       <c r="H11" t="n">
-        <v>-21.95147705078125</v>
+        <v>16.01989936828613</v>
       </c>
       <c r="I11" t="n">
-        <v>-8.13453197479248</v>
+        <v>-1.902249813079834</v>
       </c>
       <c r="J11" t="n">
-        <v>6.260873794555664</v>
+        <v>-7.0147705078125</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4583200514316559</v>
+        <v>3.738241195678711</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.726004123687744</v>
+        <v>-10.74506950378418</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.308567047119141</v>
+        <v>-7.814794063568115</v>
       </c>
       <c r="N11" t="n">
-        <v>-7.253196239471436</v>
+        <v>-7.592043399810791</v>
       </c>
       <c r="O11" t="n">
-        <v>-8.211158752441406</v>
+        <v>-3.407186031341553</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.96330714225769</v>
+        <v>-10.34259033203125</v>
       </c>
       <c r="Q11" t="n">
-        <v>73.58183288574219</v>
+        <v>80.34356689453125</v>
       </c>
       <c r="R11" t="n">
-        <v>37.73896026611328</v>
+        <v>47.51338577270508</v>
       </c>
       <c r="S11" t="n">
-        <v>35.31673431396484</v>
+        <v>32.48079299926758</v>
       </c>
       <c r="T11" t="n">
-        <v>27.05937767028809</v>
+        <v>24.49658203125</v>
       </c>
       <c r="U11" t="n">
-        <v>31.29484367370605</v>
+        <v>17.32357788085938</v>
       </c>
       <c r="V11" t="n">
-        <v>17.05021667480469</v>
+        <v>19.94320487976074</v>
       </c>
       <c r="W11" t="n">
-        <v>11.80955696105957</v>
+        <v>17.33985137939453</v>
       </c>
       <c r="X11" t="n">
-        <v>12.16705322265625</v>
+        <v>11.18221950531006</v>
       </c>
       <c r="Y11" t="n">
-        <v>11.09018230438232</v>
+        <v>12.47556400299072</v>
       </c>
       <c r="Z11" t="n">
-        <v>7.937170028686523</v>
+        <v>12.64448642730713</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.534924507141113</v>
+        <v>8.452353477478027</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.3552417755127</v>
+        <v>7.142847061157227</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.619464874267578</v>
+        <v>8.693179130554199</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>person 4</t>
+          <t>person 13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Priyal_1.ogg</t>
+          <t>roshan_2.ogg</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dataset\person 4\Priyal_1.ogg</t>
+          <t>dataset\person 13\roshan_2.ogg</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-312.5486450195312</v>
+        <v>-286.0506591796875</v>
       </c>
       <c r="E12" t="n">
-        <v>150.1796722412109</v>
+        <v>122.6934661865234</v>
       </c>
       <c r="F12" t="n">
-        <v>7.713390350341797</v>
+        <v>-8.790350914001465</v>
       </c>
       <c r="G12" t="n">
-        <v>6.145754814147949</v>
+        <v>17.76433181762695</v>
       </c>
       <c r="H12" t="n">
-        <v>3.052168369293213</v>
+        <v>12.58927631378174</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.776192665100098</v>
+        <v>-9.927440643310547</v>
       </c>
       <c r="J12" t="n">
-        <v>-9.216532707214355</v>
+        <v>-12.55085945129395</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.588597774505615</v>
+        <v>-0.07523587346076965</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.173582077026367</v>
+        <v>-12.64503955841064</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8687239289283752</v>
+        <v>-13.54410743713379</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4865387380123138</v>
+        <v>-7.181313514709473</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.973953723907471</v>
+        <v>-4.673456192016602</v>
       </c>
       <c r="P12" t="n">
-        <v>-10.27382564544678</v>
+        <v>-14.11806869506836</v>
       </c>
       <c r="Q12" t="n">
-        <v>65.61749267578125</v>
+        <v>93.43992614746094</v>
       </c>
       <c r="R12" t="n">
-        <v>37.27419281005859</v>
+        <v>45.72597885131836</v>
       </c>
       <c r="S12" t="n">
-        <v>25.96170616149902</v>
+        <v>31.81064987182617</v>
       </c>
       <c r="T12" t="n">
-        <v>21.23504829406738</v>
+        <v>25.21846771240234</v>
       </c>
       <c r="U12" t="n">
-        <v>13.79465866088867</v>
+        <v>16.7838249206543</v>
       </c>
       <c r="V12" t="n">
-        <v>16.28481674194336</v>
+        <v>20.09385871887207</v>
       </c>
       <c r="W12" t="n">
-        <v>13.23305130004883</v>
+        <v>18.32108879089355</v>
       </c>
       <c r="X12" t="n">
-        <v>10.71380233764648</v>
+        <v>12.18743133544922</v>
       </c>
       <c r="Y12" t="n">
-        <v>10.04259204864502</v>
+        <v>12.73563766479492</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.751870632171631</v>
+        <v>13.32141399383545</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.407976627349854</v>
+        <v>8.807895660400391</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.53666877746582</v>
+        <v>9.515532493591309</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.279526710510254</v>
+        <v>10.34522819519043</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>person 4</t>
+          <t>person 15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Priyal_2.ogg</t>
+          <t>ishita_1.ogg</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dataset\person 4\Priyal_2.ogg</t>
+          <t>dataset\person 15\ishita_1.ogg</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-311.0335998535156</v>
+        <v>-449.1213684082031</v>
       </c>
       <c r="E13" t="n">
-        <v>139.7058715820312</v>
+        <v>95.70502471923828</v>
       </c>
       <c r="F13" t="n">
-        <v>2.826289176940918</v>
+        <v>24.37716484069824</v>
       </c>
       <c r="G13" t="n">
-        <v>18.36519813537598</v>
+        <v>11.91084289550781</v>
       </c>
       <c r="H13" t="n">
-        <v>6.796773433685303</v>
+        <v>-17.09675788879395</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.709654569625854</v>
+        <v>-14.28932952880859</v>
       </c>
       <c r="J13" t="n">
-        <v>-10.10908794403076</v>
+        <v>-21.16751861572266</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4125159382820129</v>
+        <v>-14.43151569366455</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2676233649253845</v>
+        <v>-15.77502346038818</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4392862021923065</v>
+        <v>-11.47546195983887</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.075055122375488</v>
+        <v>-9.251642227172852</v>
       </c>
       <c r="O13" t="n">
-        <v>0.571028470993042</v>
+        <v>-1.512097716331482</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.892978668212891</v>
+        <v>-9.841765403747559</v>
       </c>
       <c r="Q13" t="n">
-        <v>70.24768829345703</v>
+        <v>105.9843215942383</v>
       </c>
       <c r="R13" t="n">
-        <v>34.07271957397461</v>
+        <v>58.58419799804688</v>
       </c>
       <c r="S13" t="n">
-        <v>29.20603370666504</v>
+        <v>49.7077751159668</v>
       </c>
       <c r="T13" t="n">
-        <v>20.54103469848633</v>
+        <v>32.83292388916016</v>
       </c>
       <c r="U13" t="n">
-        <v>13.63752746582031</v>
+        <v>25.16578674316406</v>
       </c>
       <c r="V13" t="n">
-        <v>16.40136337280273</v>
+        <v>17.93163681030273</v>
       </c>
       <c r="W13" t="n">
-        <v>13.55265617370605</v>
+        <v>17.51604843139648</v>
       </c>
       <c r="X13" t="n">
-        <v>9.749473571777344</v>
+        <v>16.58313369750977</v>
       </c>
       <c r="Y13" t="n">
-        <v>10.3587532043457</v>
+        <v>15.78795146942139</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.531620502471924</v>
+        <v>9.607026100158691</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.957065582275391</v>
+        <v>9.250849723815918</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.562671184539795</v>
+        <v>10.14445686340332</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.419523239135742</v>
+        <v>9.975936889648438</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>person 5</t>
+          <t>person 15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Shourya_1.ogg</t>
+          <t>ishita_2.ogg</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dataset\person 5\Shourya_1.ogg</t>
+          <t>dataset\person 15\ishita_2.ogg</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-358.8090515136719</v>
+        <v>-455.57470703125</v>
       </c>
       <c r="E14" t="n">
-        <v>114.3142395019531</v>
+        <v>93.03908538818359</v>
       </c>
       <c r="F14" t="n">
-        <v>37.55840682983398</v>
+        <v>29.17049789428711</v>
       </c>
       <c r="G14" t="n">
-        <v>13.92228031158447</v>
+        <v>5.298642158508301</v>
       </c>
       <c r="H14" t="n">
-        <v>1.206528663635254</v>
+        <v>-16.45624923706055</v>
       </c>
       <c r="I14" t="n">
-        <v>6.434402942657471</v>
+        <v>-10.79711818695068</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.759699821472168</v>
+        <v>-16.82701110839844</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6461262702941895</v>
+        <v>-21.24492645263672</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.814217090606689</v>
+        <v>-13.83151149749756</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.152784109115601</v>
+        <v>-7.746378898620605</v>
       </c>
       <c r="N14" t="n">
-        <v>1.124211668968201</v>
+        <v>-8.284113883972168</v>
       </c>
       <c r="O14" t="n">
-        <v>2.428881645202637</v>
+        <v>-5.428351879119873</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.400106191635132</v>
+        <v>-6.585022449493408</v>
       </c>
       <c r="Q14" t="n">
-        <v>89.46620941162109</v>
+        <v>95.24351501464844</v>
       </c>
       <c r="R14" t="n">
-        <v>61.67924499511719</v>
+        <v>57.86422348022461</v>
       </c>
       <c r="S14" t="n">
-        <v>28.91465950012207</v>
+        <v>46.74026107788086</v>
       </c>
       <c r="T14" t="n">
-        <v>31.10330772399902</v>
+        <v>33.89299774169922</v>
       </c>
       <c r="U14" t="n">
-        <v>17.80472946166992</v>
+        <v>25.53926277160645</v>
       </c>
       <c r="V14" t="n">
-        <v>16.71832847595215</v>
+        <v>18.4778938293457</v>
       </c>
       <c r="W14" t="n">
-        <v>18.56906890869141</v>
+        <v>17.08403968811035</v>
       </c>
       <c r="X14" t="n">
-        <v>13.13578224182129</v>
+        <v>17.09587287902832</v>
       </c>
       <c r="Y14" t="n">
-        <v>11.11325168609619</v>
+        <v>15.31909084320068</v>
       </c>
       <c r="Z14" t="n">
-        <v>9.236356735229492</v>
+        <v>10.73708343505859</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.45839786529541</v>
+        <v>9.422691345214844</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.519502639770508</v>
+        <v>9.350004196166992</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.712535858154297</v>
+        <v>8.414717674255371</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>person 5</t>
+          <t>person 17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Shourya_2.ogg</t>
+          <t>aayan_1.ogg</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dataset\person 5\Shourya_2.ogg</t>
+          <t>dataset\person 17\aayan_1.ogg</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-304.3930969238281</v>
+        <v>-269.2441711425781</v>
       </c>
       <c r="E15" t="n">
-        <v>110.9409027099609</v>
+        <v>126.9574203491211</v>
       </c>
       <c r="F15" t="n">
-        <v>22.86139297485352</v>
+        <v>-41.61519241333008</v>
       </c>
       <c r="G15" t="n">
-        <v>9.929296493530273</v>
+        <v>-8.922131538391113</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.179068803787231</v>
+        <v>-7.855691909790039</v>
       </c>
       <c r="I15" t="n">
-        <v>7.390394687652588</v>
+        <v>3.391450643539429</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.251555919647217</v>
+        <v>-13.76734352111816</v>
       </c>
       <c r="K15" t="n">
-        <v>5.896897792816162</v>
+        <v>-17.60487365722656</v>
       </c>
       <c r="L15" t="n">
-        <v>-3.324414491653442</v>
+        <v>-11.53079414367676</v>
       </c>
       <c r="M15" t="n">
-        <v>-7.386799335479736</v>
+        <v>-3.042881965637207</v>
       </c>
       <c r="N15" t="n">
-        <v>-4.624073505401611</v>
+        <v>-7.011881351470947</v>
       </c>
       <c r="O15" t="n">
-        <v>6.68902587890625</v>
+        <v>-9.13245677947998</v>
       </c>
       <c r="P15" t="n">
-        <v>-4.714010715484619</v>
+        <v>-10.53621673583984</v>
       </c>
       <c r="Q15" t="n">
-        <v>91.78868865966797</v>
+        <v>98.89364624023438</v>
       </c>
       <c r="R15" t="n">
-        <v>62.5364990234375</v>
+        <v>51.84964752197266</v>
       </c>
       <c r="S15" t="n">
-        <v>29.78198432922363</v>
+        <v>24.45517349243164</v>
       </c>
       <c r="T15" t="n">
-        <v>32.40509796142578</v>
+        <v>22.55305862426758</v>
       </c>
       <c r="U15" t="n">
-        <v>20.26198577880859</v>
+        <v>15.74011421203613</v>
       </c>
       <c r="V15" t="n">
-        <v>14.40401840209961</v>
+        <v>15.31006813049316</v>
       </c>
       <c r="W15" t="n">
-        <v>18.52730178833008</v>
+        <v>15.30315017700195</v>
       </c>
       <c r="X15" t="n">
-        <v>12.89473533630371</v>
+        <v>9.294642448425293</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.26882934570312</v>
+        <v>9.738674163818359</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.64115619659424</v>
+        <v>10.24271392822266</v>
       </c>
       <c r="AA15" t="n">
-        <v>10.10405349731445</v>
+        <v>7.041171073913574</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.079475402832031</v>
+        <v>6.355996131896973</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.508294105529785</v>
+        <v>6.729095935821533</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>person 6</t>
+          <t>person 17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tejender_1.ogg</t>
+          <t>aayan_2.ogg</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dataset\person 6\Tejender_1.ogg</t>
+          <t>dataset\person 17\aayan_2.ogg</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-241.2238159179688</v>
+        <v>-285.6423950195312</v>
       </c>
       <c r="E16" t="n">
-        <v>130.6345672607422</v>
+        <v>141.4721374511719</v>
       </c>
       <c r="F16" t="n">
-        <v>-12.36108493804932</v>
+        <v>-51.26475143432617</v>
       </c>
       <c r="G16" t="n">
-        <v>13.04714488983154</v>
+        <v>14.25670337677002</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2612474262714386</v>
+        <v>9.503307342529297</v>
       </c>
       <c r="I16" t="n">
-        <v>-14.38956260681152</v>
+        <v>-24.38692092895508</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.22889137268066</v>
+        <v>-19.43534469604492</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.16316032409668</v>
+        <v>2.900527000427246</v>
       </c>
       <c r="L16" t="n">
-        <v>-8.592954635620117</v>
+        <v>-19.78285026550293</v>
       </c>
       <c r="M16" t="n">
-        <v>-12.96053504943848</v>
+        <v>-7.829159259796143</v>
       </c>
       <c r="N16" t="n">
-        <v>3.854934453964233</v>
+        <v>-9.018784523010254</v>
       </c>
       <c r="O16" t="n">
-        <v>-4.597562789916992</v>
+        <v>-8.008280754089355</v>
       </c>
       <c r="P16" t="n">
-        <v>-8.279567718505859</v>
+        <v>-12.78224086761475</v>
       </c>
       <c r="Q16" t="n">
-        <v>97.86956024169922</v>
+        <v>102.0600814819336</v>
       </c>
       <c r="R16" t="n">
-        <v>57.71438980102539</v>
+        <v>51.93245697021484</v>
       </c>
       <c r="S16" t="n">
-        <v>46.75894927978516</v>
+        <v>27.7769832611084</v>
       </c>
       <c r="T16" t="n">
-        <v>32.36280822753906</v>
+        <v>26.33674049377441</v>
       </c>
       <c r="U16" t="n">
-        <v>18.50816535949707</v>
+        <v>17.13046455383301</v>
       </c>
       <c r="V16" t="n">
-        <v>22.63165855407715</v>
+        <v>15.24574661254883</v>
       </c>
       <c r="W16" t="n">
-        <v>18.74880218505859</v>
+        <v>14.14058303833008</v>
       </c>
       <c r="X16" t="n">
-        <v>11.94958877563477</v>
+        <v>10.77947425842285</v>
       </c>
       <c r="Y16" t="n">
-        <v>14.44866466522217</v>
+        <v>11.13122081756592</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.14589977264404</v>
+        <v>10.19493007659912</v>
       </c>
       <c r="AA16" t="n">
-        <v>10.23093128204346</v>
+        <v>9.176013946533203</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.25855827331543</v>
+        <v>8.550219535827637</v>
       </c>
       <c r="AC16" t="n">
-        <v>10.18418788909912</v>
+        <v>6.587140083312988</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>person 6</t>
+          <t>person 18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tejender_2.ogg</t>
+          <t>vardhan_!.ogg</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dataset\person 6\Tejender_2.ogg</t>
+          <t>dataset\person 18\vardhan_!.ogg</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-279.4379577636719</v>
+        <v>-200.0518646240234</v>
       </c>
       <c r="E17" t="n">
-        <v>133.3796234130859</v>
+        <v>112.8166275024414</v>
       </c>
       <c r="F17" t="n">
-        <v>-32.24570465087891</v>
+        <v>19.7890625</v>
       </c>
       <c r="G17" t="n">
-        <v>33.45166015625</v>
+        <v>35.81399154663086</v>
       </c>
       <c r="H17" t="n">
-        <v>20.97794532775879</v>
+        <v>3.940664529800415</v>
       </c>
       <c r="I17" t="n">
-        <v>1.798129558563232</v>
+        <v>-1.491778492927551</v>
       </c>
       <c r="J17" t="n">
-        <v>-17.07165145874023</v>
+        <v>-11.54604625701904</v>
       </c>
       <c r="K17" t="n">
-        <v>-9.722966194152832</v>
+        <v>-1.927687287330627</v>
       </c>
       <c r="L17" t="n">
-        <v>-7.129319190979004</v>
+        <v>-7.832396984100342</v>
       </c>
       <c r="M17" t="n">
-        <v>-11.12513542175293</v>
+        <v>-3.122490167617798</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7795337438583374</v>
+        <v>-6.979879379272461</v>
       </c>
       <c r="O17" t="n">
-        <v>-5.830524444580078</v>
+        <v>-1.894330501556396</v>
       </c>
       <c r="P17" t="n">
-        <v>-6.15012264251709</v>
+        <v>-5.938515663146973</v>
       </c>
       <c r="Q17" t="n">
-        <v>104.7699127197266</v>
+        <v>68.28910064697266</v>
       </c>
       <c r="R17" t="n">
-        <v>53.32034683227539</v>
+        <v>57.80504608154297</v>
       </c>
       <c r="S17" t="n">
-        <v>52.46269226074219</v>
+        <v>23.09626770019531</v>
       </c>
       <c r="T17" t="n">
-        <v>32.73448944091797</v>
+        <v>26.16904067993164</v>
       </c>
       <c r="U17" t="n">
-        <v>25.35870552062988</v>
+        <v>15.36452198028564</v>
       </c>
       <c r="V17" t="n">
-        <v>22.62563133239746</v>
+        <v>17.69928741455078</v>
       </c>
       <c r="W17" t="n">
-        <v>19.90865898132324</v>
+        <v>15.21439838409424</v>
       </c>
       <c r="X17" t="n">
-        <v>15.17664623260498</v>
+        <v>11.13945960998535</v>
       </c>
       <c r="Y17" t="n">
-        <v>15.14743232727051</v>
+        <v>13.97567653656006</v>
       </c>
       <c r="Z17" t="n">
-        <v>11.42538166046143</v>
+        <v>11.48021507263184</v>
       </c>
       <c r="AA17" t="n">
-        <v>9.400094985961914</v>
+        <v>8.638257026672363</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.645046234130859</v>
+        <v>8.92144775390625</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.31033992767334</v>
+        <v>8.279966354370117</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>person 8</t>
+          <t>person 18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ankita_1.ogg</t>
+          <t>vardhan_3.ogg</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dataset\person 8\ankita_1.ogg</t>
+          <t>dataset\person 18\vardhan_3.ogg</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-270.2237243652344</v>
+        <v>-214.8280639648438</v>
       </c>
       <c r="E18" t="n">
-        <v>58.96270751953125</v>
+        <v>112.0350799560547</v>
       </c>
       <c r="F18" t="n">
-        <v>38.67244720458984</v>
+        <v>25.18291664123535</v>
       </c>
       <c r="G18" t="n">
-        <v>8.070169448852539</v>
+        <v>27.75420761108398</v>
       </c>
       <c r="H18" t="n">
-        <v>-24.42742538452148</v>
+        <v>1.803244590759277</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1974196434021</v>
+        <v>0.9930463433265686</v>
       </c>
       <c r="J18" t="n">
-        <v>-7.311805248260498</v>
+        <v>-9.322339057922363</v>
       </c>
       <c r="K18" t="n">
-        <v>-10.53012466430664</v>
+        <v>0.6462122201919556</v>
       </c>
       <c r="L18" t="n">
-        <v>-5.142326354980469</v>
+        <v>-9.968441009521484</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.67604398727417</v>
+        <v>-1.917246103286743</v>
       </c>
       <c r="N18" t="n">
-        <v>-12.98607063293457</v>
+        <v>-4.38447904586792</v>
       </c>
       <c r="O18" t="n">
-        <v>-10.37759876251221</v>
+        <v>-3.10486102104187</v>
       </c>
       <c r="P18" t="n">
-        <v>-8.26213550567627</v>
+        <v>-6.121625900268555</v>
       </c>
       <c r="Q18" t="n">
-        <v>122.35009765625</v>
+        <v>70.03459167480469</v>
       </c>
       <c r="R18" t="n">
-        <v>53.08518600463867</v>
+        <v>59.11071014404297</v>
       </c>
       <c r="S18" t="n">
-        <v>39.09588241577148</v>
+        <v>23.29788970947266</v>
       </c>
       <c r="T18" t="n">
-        <v>27.46438217163086</v>
+        <v>21.87420463562012</v>
       </c>
       <c r="U18" t="n">
-        <v>28.98434257507324</v>
+        <v>15.16538715362549</v>
       </c>
       <c r="V18" t="n">
-        <v>15.67507457733154</v>
+        <v>17.90091323852539</v>
       </c>
       <c r="W18" t="n">
-        <v>14.56611728668213</v>
+        <v>15.09103012084961</v>
       </c>
       <c r="X18" t="n">
-        <v>14.58829212188721</v>
+        <v>9.848606109619141</v>
       </c>
       <c r="Y18" t="n">
-        <v>12.29934310913086</v>
+        <v>13.61015892028809</v>
       </c>
       <c r="Z18" t="n">
-        <v>10.6221866607666</v>
+        <v>9.866971015930176</v>
       </c>
       <c r="AA18" t="n">
-        <v>10.70013236999512</v>
+        <v>8.218813896179199</v>
       </c>
       <c r="AB18" t="n">
-        <v>10.061936378479</v>
+        <v>8.579716682434082</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.220752716064453</v>
+        <v>7.417625904083252</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>person 8</t>
+          <t>person 18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ankita_2.ogg</t>
+          <t>vardhan_4.ogg</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dataset\person 8\ankita_2.ogg</t>
+          <t>dataset\person 18\vardhan_4.ogg</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-250.0560913085938</v>
+        <v>-208.1157073974609</v>
       </c>
       <c r="E19" t="n">
-        <v>72.12837219238281</v>
+        <v>110.7679824829102</v>
       </c>
       <c r="F19" t="n">
-        <v>34.50404357910156</v>
+        <v>20.411376953125</v>
       </c>
       <c r="G19" t="n">
-        <v>5.64661693572998</v>
+        <v>35.89154052734375</v>
       </c>
       <c r="H19" t="n">
-        <v>-31.13961982727051</v>
+        <v>8.700310707092285</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.317376494407654</v>
+        <v>-3.669002056121826</v>
       </c>
       <c r="J19" t="n">
-        <v>-10.20572566986084</v>
+        <v>-12.10101413726807</v>
       </c>
       <c r="K19" t="n">
-        <v>-14.19919300079346</v>
+        <v>1.93730354309082</v>
       </c>
       <c r="L19" t="n">
-        <v>-4.693023681640625</v>
+        <v>-10.17233085632324</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.679990768432617</v>
+        <v>-3.630261898040771</v>
       </c>
       <c r="N19" t="n">
-        <v>-15.13342761993408</v>
+        <v>-6.409022808074951</v>
       </c>
       <c r="O19" t="n">
-        <v>-7.792290687561035</v>
+        <v>-2.838922023773193</v>
       </c>
       <c r="P19" t="n">
-        <v>-9.90543270111084</v>
+        <v>-6.336955547332764</v>
       </c>
       <c r="Q19" t="n">
-        <v>119.1896743774414</v>
+        <v>72.87003326416016</v>
       </c>
       <c r="R19" t="n">
-        <v>51.60607147216797</v>
+        <v>58.94798278808594</v>
       </c>
       <c r="S19" t="n">
-        <v>37.96743011474609</v>
+        <v>22.40644454956055</v>
       </c>
       <c r="T19" t="n">
-        <v>28.75864028930664</v>
+        <v>22.25759124755859</v>
       </c>
       <c r="U19" t="n">
-        <v>29.4977855682373</v>
+        <v>13.994704246521</v>
       </c>
       <c r="V19" t="n">
-        <v>17.02374649047852</v>
+        <v>17.92287826538086</v>
       </c>
       <c r="W19" t="n">
-        <v>14.97891616821289</v>
+        <v>15.98887920379639</v>
       </c>
       <c r="X19" t="n">
-        <v>14.13392162322998</v>
+        <v>10.27779960632324</v>
       </c>
       <c r="Y19" t="n">
-        <v>12.5789794921875</v>
+        <v>12.41474151611328</v>
       </c>
       <c r="Z19" t="n">
-        <v>10.51625442504883</v>
+        <v>10.22132682800293</v>
       </c>
       <c r="AA19" t="n">
-        <v>10.5496711730957</v>
+        <v>8.701549530029297</v>
       </c>
       <c r="AB19" t="n">
-        <v>9.269749641418457</v>
+        <v>7.781230926513672</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.096851348876953</v>
+        <v>7.972690105438232</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>person 8</t>
+          <t>person 19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ankita_4.ogg</t>
+          <t>darshil_1.ogg</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dataset\person 8\ankita_4.ogg</t>
+          <t>dataset\person 19\darshil_1.ogg</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-258.3805236816406</v>
+        <v>-394.994384765625</v>
       </c>
       <c r="E20" t="n">
-        <v>92.83200073242188</v>
+        <v>104.7689971923828</v>
       </c>
       <c r="F20" t="n">
-        <v>11.39120864868164</v>
+        <v>28.20153045654297</v>
       </c>
       <c r="G20" t="n">
-        <v>6.207101821899414</v>
+        <v>9.572109222412109</v>
       </c>
       <c r="H20" t="n">
-        <v>2.089468240737915</v>
+        <v>18.06620216369629</v>
       </c>
       <c r="I20" t="n">
-        <v>-20.39954376220703</v>
+        <v>5.220097064971924</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.28644371032715</v>
+        <v>-16.86857414245605</v>
       </c>
       <c r="K20" t="n">
-        <v>-8.85013484954834</v>
+        <v>-10.91190433502197</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6754090785980225</v>
+        <v>0.5973178744316101</v>
       </c>
       <c r="M20" t="n">
-        <v>-11.15882301330566</v>
+        <v>-6.023237705230713</v>
       </c>
       <c r="N20" t="n">
-        <v>-12.50483322143555</v>
+        <v>-5.479997158050537</v>
       </c>
       <c r="O20" t="n">
-        <v>-8.705537796020508</v>
+        <v>-1.450215935707092</v>
       </c>
       <c r="P20" t="n">
-        <v>-8.155506134033203</v>
+        <v>-6.827906608581543</v>
       </c>
       <c r="Q20" t="n">
-        <v>106.4656829833984</v>
+        <v>127.8232040405273</v>
       </c>
       <c r="R20" t="n">
-        <v>48.88466262817383</v>
+        <v>65.19478607177734</v>
       </c>
       <c r="S20" t="n">
-        <v>35.45600891113281</v>
+        <v>32.58731842041016</v>
       </c>
       <c r="T20" t="n">
-        <v>32.61907577514648</v>
+        <v>21.05306434631348</v>
       </c>
       <c r="U20" t="n">
-        <v>22.51460838317871</v>
+        <v>16.99415969848633</v>
       </c>
       <c r="V20" t="n">
-        <v>20.42388534545898</v>
+        <v>12.99966049194336</v>
       </c>
       <c r="W20" t="n">
-        <v>14.98693084716797</v>
+        <v>20.91626739501953</v>
       </c>
       <c r="X20" t="n">
-        <v>14.11903953552246</v>
+        <v>13.9838171005249</v>
       </c>
       <c r="Y20" t="n">
-        <v>14.4618616104126</v>
+        <v>12.62128067016602</v>
       </c>
       <c r="Z20" t="n">
-        <v>9.938737869262695</v>
+        <v>14.37989234924316</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.666037559509277</v>
+        <v>10.52409362792969</v>
       </c>
       <c r="AB20" t="n">
-        <v>10.90330410003662</v>
+        <v>6.949148654937744</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.622568130493164</v>
+        <v>10.80532073974609</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>person 9</t>
+          <t>person 19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>vaishnavi_1.ogg</t>
+          <t>darshil_3.ogg</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dataset\person 9\vaishnavi_1.ogg</t>
+          <t>dataset\person 19\darshil_3.ogg</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-256.3796081542969</v>
+        <v>-350.5903930664062</v>
       </c>
       <c r="E21" t="n">
-        <v>98.49275970458984</v>
+        <v>121.4785766601562</v>
       </c>
       <c r="F21" t="n">
-        <v>8.732111930847168</v>
+        <v>19.89072227478027</v>
       </c>
       <c r="G21" t="n">
-        <v>30.44884872436523</v>
+        <v>14.91202068328857</v>
       </c>
       <c r="H21" t="n">
-        <v>-7.923402309417725</v>
+        <v>14.1753568649292</v>
       </c>
       <c r="I21" t="n">
-        <v>-7.455092430114746</v>
+        <v>-1.248007416725159</v>
       </c>
       <c r="J21" t="n">
-        <v>-19.39515495300293</v>
+        <v>-18.9353199005127</v>
       </c>
       <c r="K21" t="n">
-        <v>-19.24704360961914</v>
+        <v>-15.67662525177002</v>
       </c>
       <c r="L21" t="n">
-        <v>-4.155113697052002</v>
+        <v>0.8180702328681946</v>
       </c>
       <c r="M21" t="n">
-        <v>-9.748040199279785</v>
+        <v>-8.96541690826416</v>
       </c>
       <c r="N21" t="n">
-        <v>-8.807007789611816</v>
+        <v>-6.502516746520996</v>
       </c>
       <c r="O21" t="n">
-        <v>-6.999690055847168</v>
+        <v>-3.261698961257935</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4338657259941101</v>
+        <v>-8.551376342773438</v>
       </c>
       <c r="Q21" t="n">
-        <v>121.5381088256836</v>
+        <v>124.7190246582031</v>
       </c>
       <c r="R21" t="n">
-        <v>39.5520133972168</v>
+        <v>65.27979278564453</v>
       </c>
       <c r="S21" t="n">
-        <v>45.04905700683594</v>
+        <v>42.47555160522461</v>
       </c>
       <c r="T21" t="n">
-        <v>25.2275562286377</v>
+        <v>27.35028648376465</v>
       </c>
       <c r="U21" t="n">
-        <v>26.77007865905762</v>
+        <v>23.79360961914062</v>
       </c>
       <c r="V21" t="n">
-        <v>13.50710296630859</v>
+        <v>14.9731559753418</v>
       </c>
       <c r="W21" t="n">
-        <v>14.61097717285156</v>
+        <v>21.5970516204834</v>
       </c>
       <c r="X21" t="n">
-        <v>15.18807888031006</v>
+        <v>15.83456993103027</v>
       </c>
       <c r="Y21" t="n">
-        <v>13.30795669555664</v>
+        <v>14.10674095153809</v>
       </c>
       <c r="Z21" t="n">
-        <v>11.20494937896729</v>
+        <v>14.15629482269287</v>
       </c>
       <c r="AA21" t="n">
-        <v>10.87530899047852</v>
+        <v>11.94312286376953</v>
       </c>
       <c r="AB21" t="n">
-        <v>11.49388599395752</v>
+        <v>7.948626041412354</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.31267261505127</v>
+        <v>10.45221328735352</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>person 19</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>darshil_4.ogg</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>dataset\person 19\darshil_4.ogg</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-349.9657897949219</v>
+      </c>
+      <c r="E22" t="n">
+        <v>101.3003387451172</v>
+      </c>
+      <c r="F22" t="n">
+        <v>22.75123596191406</v>
+      </c>
+      <c r="G22" t="n">
+        <v>18.4917106628418</v>
+      </c>
+      <c r="H22" t="n">
+        <v>12.29379081726074</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.4402470886707306</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-15.75422668457031</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-16.77762031555176</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-4.829863548278809</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-10.01693439483643</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-8.100065231323242</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-4.677578449249268</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-10.25537967681885</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>123.7704925537109</v>
+      </c>
+      <c r="R22" t="n">
+        <v>69.43382263183594</v>
+      </c>
+      <c r="S22" t="n">
+        <v>40.89107131958008</v>
+      </c>
+      <c r="T22" t="n">
+        <v>30.06784629821777</v>
+      </c>
+      <c r="U22" t="n">
+        <v>20.65502166748047</v>
+      </c>
+      <c r="V22" t="n">
+        <v>16.78813171386719</v>
+      </c>
+      <c r="W22" t="n">
+        <v>17.59750938415527</v>
+      </c>
+      <c r="X22" t="n">
+        <v>15.89231395721436</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>11.68994617462158</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>15.30501842498779</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>11.4362325668335</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>8.793610572814941</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>11.44991874694824</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>person 2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Harshita_1.ogg</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>dataset\person 2\Harshita_1.ogg</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-286.7710876464844</v>
+      </c>
+      <c r="E23" t="n">
+        <v>145.6819763183594</v>
+      </c>
+      <c r="F23" t="n">
+        <v>36.14165115356445</v>
+      </c>
+      <c r="G23" t="n">
+        <v>19.86843681335449</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-16.67756271362305</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-3.458644866943359</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.599449872970581</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-7.693424224853516</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-3.980954647064209</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.4789998531341553</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-6.25227689743042</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-2.499890089035034</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-2.321202993392944</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>65.44059753417969</v>
+      </c>
+      <c r="R23" t="n">
+        <v>41.9994010925293</v>
+      </c>
+      <c r="S23" t="n">
+        <v>27.22202301025391</v>
+      </c>
+      <c r="T23" t="n">
+        <v>22.62238502502441</v>
+      </c>
+      <c r="U23" t="n">
+        <v>16.1590576171875</v>
+      </c>
+      <c r="V23" t="n">
+        <v>13.40995788574219</v>
+      </c>
+      <c r="W23" t="n">
+        <v>9.408201217651367</v>
+      </c>
+      <c r="X23" t="n">
+        <v>13.32199478149414</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>10.54885101318359</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>8.566182136535645</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>8.690876960754395</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>8.26371955871582</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>6.744489192962646</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>person 2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Harshita_2.ogg</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>dataset\person 2\Harshita_2.ogg</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-285.5520935058594</v>
+      </c>
+      <c r="E24" t="n">
+        <v>146.4192199707031</v>
+      </c>
+      <c r="F24" t="n">
+        <v>31.81262016296387</v>
+      </c>
+      <c r="G24" t="n">
+        <v>19.22633743286133</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-12.10067462921143</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-2.464438676834106</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.2841993570327759</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-6.251331329345703</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-1.298632860183716</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.6891754865646362</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-9.162246704101562</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.03717708215117455</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-1.480612277984619</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>64.51747131347656</v>
+      </c>
+      <c r="R24" t="n">
+        <v>45.21198654174805</v>
+      </c>
+      <c r="S24" t="n">
+        <v>28.2469482421875</v>
+      </c>
+      <c r="T24" t="n">
+        <v>22.09764671325684</v>
+      </c>
+      <c r="U24" t="n">
+        <v>15.96239948272705</v>
+      </c>
+      <c r="V24" t="n">
+        <v>13.65683841705322</v>
+      </c>
+      <c r="W24" t="n">
+        <v>9.648412704467773</v>
+      </c>
+      <c r="X24" t="n">
+        <v>14.66029357910156</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>11.09800815582275</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>7.877726554870605</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>8.673047065734863</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>8.800985336303711</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>6.93620777130127</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>person 20</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>tia_!.ogg</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>dataset\person 20\tia_!.ogg</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-389.9906005859375</v>
+      </c>
+      <c r="E25" t="n">
+        <v>128.6345977783203</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5.27173376083374</v>
+      </c>
+      <c r="G25" t="n">
+        <v>13.51928234100342</v>
+      </c>
+      <c r="H25" t="n">
+        <v>12.11761856079102</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-10.39479637145996</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-24.09167861938477</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-14.72308540344238</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-10.71997737884521</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-3.853574275970459</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-7.452871322631836</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-5.367785930633545</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-5.084888458251953</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>44.89416122436523</v>
+      </c>
+      <c r="R25" t="n">
+        <v>38.05389404296875</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25.1969108581543</v>
+      </c>
+      <c r="T25" t="n">
+        <v>16.15860557556152</v>
+      </c>
+      <c r="U25" t="n">
+        <v>15.43584156036377</v>
+      </c>
+      <c r="V25" t="n">
+        <v>10.628005027771</v>
+      </c>
+      <c r="W25" t="n">
+        <v>9.763632774353027</v>
+      </c>
+      <c r="X25" t="n">
+        <v>8.919713973999023</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>9.020009994506836</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5.734650135040283</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>6.028921604156494</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>6.126997470855713</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>5.981704711914062</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>person 20</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>tia_2.ogg</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>dataset\person 20\tia_2.ogg</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>-391.7303466796875</v>
+      </c>
+      <c r="E26" t="n">
+        <v>123.0383148193359</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.519901275634766</v>
+      </c>
+      <c r="G26" t="n">
+        <v>14.73026180267334</v>
+      </c>
+      <c r="H26" t="n">
+        <v>11.74123764038086</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-7.9287428855896</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-22.32376289367676</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-15.02742481231689</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-9.044745445251465</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-2.3067786693573</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-6.779703617095947</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-5.20822286605835</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-4.483644485473633</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>51.14272689819336</v>
+      </c>
+      <c r="R26" t="n">
+        <v>37.01113891601562</v>
+      </c>
+      <c r="S26" t="n">
+        <v>24.58556365966797</v>
+      </c>
+      <c r="T26" t="n">
+        <v>17.9415283203125</v>
+      </c>
+      <c r="U26" t="n">
+        <v>15.3988618850708</v>
+      </c>
+      <c r="V26" t="n">
+        <v>12.00592041015625</v>
+      </c>
+      <c r="W26" t="n">
+        <v>11.1993989944458</v>
+      </c>
+      <c r="X26" t="n">
+        <v>8.783780097961426</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>9.7567138671875</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>5.985620498657227</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>6.670583724975586</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>6.572318553924561</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>6.912961006164551</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>person 21</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>yash_1.ogg</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>dataset\person 21\yash_1.ogg</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-285.1409606933594</v>
+      </c>
+      <c r="E27" t="n">
+        <v>111.358024597168</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-7.675256252288818</v>
+      </c>
+      <c r="G27" t="n">
+        <v>28.59347343444824</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-12.57236862182617</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-10.66905403137207</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-15.783935546875</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-17.50099182128906</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-18.3094367980957</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-8.77493953704834</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-9.895393371582031</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-8.36782169342041</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-7.130707740783691</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>98.66203308105469</v>
+      </c>
+      <c r="R27" t="n">
+        <v>53.25146484375</v>
+      </c>
+      <c r="S27" t="n">
+        <v>37.29780197143555</v>
+      </c>
+      <c r="T27" t="n">
+        <v>37.33657073974609</v>
+      </c>
+      <c r="U27" t="n">
+        <v>21.96623611450195</v>
+      </c>
+      <c r="V27" t="n">
+        <v>16.48222923278809</v>
+      </c>
+      <c r="W27" t="n">
+        <v>15.87715435028076</v>
+      </c>
+      <c r="X27" t="n">
+        <v>14.98569011688232</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>16.33315658569336</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>13.88424015045166</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>11.33092594146729</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>11.02672004699707</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.984439849853516</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>person 21</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>yash_2.ogg</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>dataset\person 21\yash_2.ogg</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>-264.9918518066406</v>
+      </c>
+      <c r="E28" t="n">
+        <v>99.59583282470703</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-4.292967319488525</v>
+      </c>
+      <c r="G28" t="n">
+        <v>21.63481521606445</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-14.10290718078613</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-13.52094078063965</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-19.11762809753418</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-21.04447174072266</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-15.42272758483887</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-9.444038391113281</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-9.182305335998535</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-6.810607433319092</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-6.335980415344238</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>81.72145080566406</v>
+      </c>
+      <c r="R28" t="n">
+        <v>44.39864349365234</v>
+      </c>
+      <c r="S28" t="n">
+        <v>32.9868278503418</v>
+      </c>
+      <c r="T28" t="n">
+        <v>33.1818962097168</v>
+      </c>
+      <c r="U28" t="n">
+        <v>23.00302886962891</v>
+      </c>
+      <c r="V28" t="n">
+        <v>15.72253036499023</v>
+      </c>
+      <c r="W28" t="n">
+        <v>14.67026805877686</v>
+      </c>
+      <c r="X28" t="n">
+        <v>16.11211013793945</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>15.55652904510498</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>12.45159530639648</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>10.54498672485352</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>9.944865226745605</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>9.632919311523438</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>person 21</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>yash_3.ogg</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>dataset\person 21\yash_3.ogg</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>-314.7654724121094</v>
+      </c>
+      <c r="E29" t="n">
+        <v>96.23439025878906</v>
+      </c>
+      <c r="F29" t="n">
+        <v>7.988540649414062</v>
+      </c>
+      <c r="G29" t="n">
+        <v>26.95756149291992</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-8.630905151367188</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-10.84980392456055</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-14.22557353973389</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-18.93441963195801</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-15.68928623199463</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-8.643736839294434</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-6.370185852050781</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-9.227523803710938</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-4.245995998382568</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>83.04597473144531</v>
+      </c>
+      <c r="R29" t="n">
+        <v>46.00118255615234</v>
+      </c>
+      <c r="S29" t="n">
+        <v>35.38057708740234</v>
+      </c>
+      <c r="T29" t="n">
+        <v>36.38809585571289</v>
+      </c>
+      <c r="U29" t="n">
+        <v>20.18946266174316</v>
+      </c>
+      <c r="V29" t="n">
+        <v>16.80081558227539</v>
+      </c>
+      <c r="W29" t="n">
+        <v>15.24263191223145</v>
+      </c>
+      <c r="X29" t="n">
+        <v>14.22119045257568</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>15.52142238616943</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>12.86816692352295</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>9.30838680267334</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>10.21274471282959</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8.249881744384766</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>person 22</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>pawni_1.ogg</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>dataset\person 22\pawni_1.ogg</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>-263.4427185058594</v>
+      </c>
+      <c r="E30" t="n">
+        <v>117.168586730957</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.832453489303589</v>
+      </c>
+      <c r="G30" t="n">
+        <v>21.19698143005371</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-15.02691650390625</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.320546984672546</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-17.04412078857422</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-0.7882906794548035</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-21.02290344238281</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-12.87244415283203</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-13.14768600463867</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-6.154983043670654</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-8.043229103088379</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>49.34055709838867</v>
+      </c>
+      <c r="R30" t="n">
+        <v>32.64682388305664</v>
+      </c>
+      <c r="S30" t="n">
+        <v>21.95605850219727</v>
+      </c>
+      <c r="T30" t="n">
+        <v>16.9445629119873</v>
+      </c>
+      <c r="U30" t="n">
+        <v>17.75736427307129</v>
+      </c>
+      <c r="V30" t="n">
+        <v>11.84698295593262</v>
+      </c>
+      <c r="W30" t="n">
+        <v>14.07671451568604</v>
+      </c>
+      <c r="X30" t="n">
+        <v>9.30080509185791</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>9.739677429199219</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>6.353628635406494</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>6.383163928985596</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>6.205202102661133</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>6.542716026306152</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>person 22</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>pawni_2.ogg</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>dataset\person 22\pawni_2.ogg</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>-230.1638946533203</v>
+      </c>
+      <c r="E31" t="n">
+        <v>105.4921264648438</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.159988284111023</v>
+      </c>
+      <c r="G31" t="n">
+        <v>16.20648956298828</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-22.4896354675293</v>
+      </c>
+      <c r="I31" t="n">
+        <v>10.00742626190186</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-24.39411544799805</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-5.561285495758057</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-19.61528778076172</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-17.17599678039551</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-7.076179027557373</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-10.85336685180664</v>
+      </c>
+      <c r="P31" t="n">
+        <v>-4.77818775177002</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>62.84669494628906</v>
+      </c>
+      <c r="R31" t="n">
+        <v>37.98947525024414</v>
+      </c>
+      <c r="S31" t="n">
+        <v>28.51221466064453</v>
+      </c>
+      <c r="T31" t="n">
+        <v>22.70761489868164</v>
+      </c>
+      <c r="U31" t="n">
+        <v>22.37103652954102</v>
+      </c>
+      <c r="V31" t="n">
+        <v>13.51257133483887</v>
+      </c>
+      <c r="W31" t="n">
+        <v>16.08309364318848</v>
+      </c>
+      <c r="X31" t="n">
+        <v>11.64758682250977</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>10.14969921112061</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>8.163833618164062</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>8.900728225708008</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>8.712334632873535</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>7.829525470733643</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>person 23</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ayush_1.ogg</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>dataset\person 23\ayush_1.ogg</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>-285.3861389160156</v>
+      </c>
+      <c r="E32" t="n">
+        <v>87.76021575927734</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-11.04197025299072</v>
+      </c>
+      <c r="G32" t="n">
+        <v>69.67429351806641</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-3.611426830291748</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-28.95725059509277</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-0.8586370348930359</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-7.179065227508545</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-10.82801818847656</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-7.433506011962891</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-6.531572341918945</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-13.01035022735596</v>
+      </c>
+      <c r="P32" t="n">
+        <v>-0.9246292114257812</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>106.0477523803711</v>
+      </c>
+      <c r="R32" t="n">
+        <v>57.05118179321289</v>
+      </c>
+      <c r="S32" t="n">
+        <v>40.06080627441406</v>
+      </c>
+      <c r="T32" t="n">
+        <v>37.86106109619141</v>
+      </c>
+      <c r="U32" t="n">
+        <v>25.56239318847656</v>
+      </c>
+      <c r="V32" t="n">
+        <v>23.968505859375</v>
+      </c>
+      <c r="W32" t="n">
+        <v>17.89392852783203</v>
+      </c>
+      <c r="X32" t="n">
+        <v>14.98968696594238</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>15.18694496154785</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>12.70719337463379</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>11.43594074249268</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>10.15415954589844</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>10.58498287200928</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>person 23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ayush_2.ogg</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>dataset\person 23\ayush_2.ogg</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>-385.0401611328125</v>
+      </c>
+      <c r="E33" t="n">
+        <v>76.71154022216797</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-2.947483062744141</v>
+      </c>
+      <c r="G33" t="n">
+        <v>54.31930923461914</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-4.805678367614746</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-7.329330444335938</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.3055852055549622</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-14.93986415863037</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-1.650665521621704</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-15.48281860351562</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-11.50465488433838</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-3.528943061828613</v>
+      </c>
+      <c r="P33" t="n">
+        <v>-12.76644992828369</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>132.0279388427734</v>
+      </c>
+      <c r="R33" t="n">
+        <v>56.47714614868164</v>
+      </c>
+      <c r="S33" t="n">
+        <v>40.83449172973633</v>
+      </c>
+      <c r="T33" t="n">
+        <v>41.04298400878906</v>
+      </c>
+      <c r="U33" t="n">
+        <v>24.03460502624512</v>
+      </c>
+      <c r="V33" t="n">
+        <v>19.54782104492188</v>
+      </c>
+      <c r="W33" t="n">
+        <v>15.48023509979248</v>
+      </c>
+      <c r="X33" t="n">
+        <v>16.98485946655273</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>12.45744132995605</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>14.54727554321289</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>10.56304550170898</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>10.32905673980713</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>12.3538818359375</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>person 25</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>yuvraj_1.ogg</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>dataset\person 25\yuvraj_1.ogg</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>-369.9412231445312</v>
+      </c>
+      <c r="E34" t="n">
+        <v>75.88608551025391</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4.928417205810547</v>
+      </c>
+      <c r="G34" t="n">
+        <v>30.0957202911377</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.5499467849731445</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-0.1383561342954636</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-6.192996501922607</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-11.9271993637085</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-10.80370998382568</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-10.94717693328857</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-10.88335609436035</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-6.296810626983643</v>
+      </c>
+      <c r="P34" t="n">
+        <v>-8.13135814666748</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>100.3417434692383</v>
+      </c>
+      <c r="R34" t="n">
+        <v>45.73802185058594</v>
+      </c>
+      <c r="S34" t="n">
+        <v>26.53985786437988</v>
+      </c>
+      <c r="T34" t="n">
+        <v>37.00262451171875</v>
+      </c>
+      <c r="U34" t="n">
+        <v>15.90604114532471</v>
+      </c>
+      <c r="V34" t="n">
+        <v>15.19878482818604</v>
+      </c>
+      <c r="W34" t="n">
+        <v>15.74413013458252</v>
+      </c>
+      <c r="X34" t="n">
+        <v>13.94266796112061</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>11.57063770294189</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>10.67259979248047</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>9.635258674621582</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>10.10628509521484</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>10.0682487487793</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>person 25</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>yuvraj_2.ogg</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>dataset\person 25\yuvraj_2.ogg</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>-361.8735656738281</v>
+      </c>
+      <c r="E35" t="n">
+        <v>97.45887756347656</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-8.78232479095459</v>
+      </c>
+      <c r="G35" t="n">
+        <v>36.23246383666992</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.7650606036186218</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-0.81516432762146</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-11.17895889282227</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-14.82610607147217</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-9.752766609191895</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-13.98105144500732</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-15.96403121948242</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-2.975361824035645</v>
+      </c>
+      <c r="P35" t="n">
+        <v>-7.782024383544922</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>109.9257507324219</v>
+      </c>
+      <c r="R35" t="n">
+        <v>47.06922912597656</v>
+      </c>
+      <c r="S35" t="n">
+        <v>31.25499153137207</v>
+      </c>
+      <c r="T35" t="n">
+        <v>37.61059188842773</v>
+      </c>
+      <c r="U35" t="n">
+        <v>16.09797477722168</v>
+      </c>
+      <c r="V35" t="n">
+        <v>14.41735076904297</v>
+      </c>
+      <c r="W35" t="n">
+        <v>17.23455619812012</v>
+      </c>
+      <c r="X35" t="n">
+        <v>12.80925941467285</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>11.21812534332275</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>12.25879001617432</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>12.43208789825439</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>9.741679191589355</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>9.854705810546875</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>person 26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>anushka_1.ogg</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>dataset\person 26\anushka_1.ogg</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>-349.9544372558594</v>
+      </c>
+      <c r="E36" t="n">
+        <v>111.3209915161133</v>
+      </c>
+      <c r="F36" t="n">
+        <v>11.98223400115967</v>
+      </c>
+      <c r="G36" t="n">
+        <v>34.16227340698242</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-8.403597831726074</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-1.477413892745972</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-23.84000015258789</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-20.08888053894043</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-0.6277058720588684</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-14.74545669555664</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-10.90371799468994</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-9.870601654052734</v>
+      </c>
+      <c r="P36" t="n">
+        <v>-6.933578014373779</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>74.37460327148438</v>
+      </c>
+      <c r="R36" t="n">
+        <v>45.54093170166016</v>
+      </c>
+      <c r="S36" t="n">
+        <v>36.90501022338867</v>
+      </c>
+      <c r="T36" t="n">
+        <v>33.02091598510742</v>
+      </c>
+      <c r="U36" t="n">
+        <v>26.03872871398926</v>
+      </c>
+      <c r="V36" t="n">
+        <v>13.57944011688232</v>
+      </c>
+      <c r="W36" t="n">
+        <v>16.75175285339355</v>
+      </c>
+      <c r="X36" t="n">
+        <v>14.37323665618896</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>13.14782524108887</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>10.46415710449219</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>10.34576606750488</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>10.22913551330566</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>7.606988430023193</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>person 26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>anushka_2.ogg</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>dataset\person 26\anushka_2.ogg</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>-335.5666809082031</v>
+      </c>
+      <c r="E37" t="n">
+        <v>102.0999526977539</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.255163192749023</v>
+      </c>
+      <c r="G37" t="n">
+        <v>21.43264770507812</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-12.93393039703369</v>
+      </c>
+      <c r="I37" t="n">
+        <v>4.334719657897949</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-22.13949584960938</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-24.24750709533691</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-4.421738147735596</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-14.4063081741333</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-6.027122020721436</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-6.551993846893311</v>
+      </c>
+      <c r="P37" t="n">
+        <v>-1.063975930213928</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>88.20363616943359</v>
+      </c>
+      <c r="R37" t="n">
+        <v>43.40456390380859</v>
+      </c>
+      <c r="S37" t="n">
+        <v>42.07583618164062</v>
+      </c>
+      <c r="T37" t="n">
+        <v>29.33563423156738</v>
+      </c>
+      <c r="U37" t="n">
+        <v>28.62681579589844</v>
+      </c>
+      <c r="V37" t="n">
+        <v>14.87688255310059</v>
+      </c>
+      <c r="W37" t="n">
+        <v>16.17331695556641</v>
+      </c>
+      <c r="X37" t="n">
+        <v>16.01498031616211</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>14.72065448760986</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>12.09894943237305</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>9.674441337585449</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>9.348865509033203</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>9.800844192504883</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>person 27</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>lakshya_1.ogg</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>dataset\person 27\lakshya_1.ogg</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>-272.2121887207031</v>
+      </c>
+      <c r="E38" t="n">
+        <v>124.1413955688477</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-11.09482669830322</v>
+      </c>
+      <c r="G38" t="n">
+        <v>22.71454811096191</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.931150197982788</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-11.56363964080811</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-8.367151260375977</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-20.90828514099121</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-8.502992630004883</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-8.630528450012207</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-17.3436164855957</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-3.063955783843994</v>
+      </c>
+      <c r="P38" t="n">
+        <v>-15.98363304138184</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>100.1909332275391</v>
+      </c>
+      <c r="R38" t="n">
+        <v>52.26206207275391</v>
+      </c>
+      <c r="S38" t="n">
+        <v>41.45901870727539</v>
+      </c>
+      <c r="T38" t="n">
+        <v>28.30581665039062</v>
+      </c>
+      <c r="U38" t="n">
+        <v>26.66611671447754</v>
+      </c>
+      <c r="V38" t="n">
+        <v>20.40398788452148</v>
+      </c>
+      <c r="W38" t="n">
+        <v>15.92236709594727</v>
+      </c>
+      <c r="X38" t="n">
+        <v>19.18020057678223</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>13.09757423400879</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>12.49332618713379</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>10.50527763366699</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>11.37388038635254</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>8.942444801330566</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>person 27</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>lakshya_3.ogg</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>dataset\person 27\lakshya_3.ogg</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>-273.9794006347656</v>
+      </c>
+      <c r="E39" t="n">
+        <v>104.3974685668945</v>
+      </c>
+      <c r="F39" t="n">
+        <v>15.06923007965088</v>
+      </c>
+      <c r="G39" t="n">
+        <v>23.38393402099609</v>
+      </c>
+      <c r="H39" t="n">
+        <v>6.984471321105957</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-15.20692443847656</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-13.75981998443604</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-13.48714256286621</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-12.53374481201172</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-8.845122337341309</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-11.72890949249268</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-5.458150863647461</v>
+      </c>
+      <c r="P39" t="n">
+        <v>-12.94491291046143</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>103.6448059082031</v>
+      </c>
+      <c r="R39" t="n">
+        <v>56.06024551391602</v>
+      </c>
+      <c r="S39" t="n">
+        <v>34.02785873413086</v>
+      </c>
+      <c r="T39" t="n">
+        <v>23.15749549865723</v>
+      </c>
+      <c r="U39" t="n">
+        <v>20.50190162658691</v>
+      </c>
+      <c r="V39" t="n">
+        <v>21.11351013183594</v>
+      </c>
+      <c r="W39" t="n">
+        <v>15.73110580444336</v>
+      </c>
+      <c r="X39" t="n">
+        <v>17.44620895385742</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>12.4521951675415</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>11.01986885070801</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>8.505847930908203</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>9.52967643737793</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>8.705502510070801</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>person 27</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>lakshya_4.ogg</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>dataset\person 27\lakshya_4.ogg</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>-258.4074401855469</v>
+      </c>
+      <c r="E40" t="n">
+        <v>124.6931610107422</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-16.57731437683105</v>
+      </c>
+      <c r="G40" t="n">
+        <v>25.85388565063477</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.009314775466919</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-17.78352355957031</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-9.855069160461426</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-19.74354553222656</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-9.762148857116699</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-7.278432369232178</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-12.75746917724609</v>
+      </c>
+      <c r="O40" t="n">
+        <v>-2.292094707489014</v>
+      </c>
+      <c r="P40" t="n">
+        <v>-12.09728336334229</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>94.64045715332031</v>
+      </c>
+      <c r="R40" t="n">
+        <v>47.6994743347168</v>
+      </c>
+      <c r="S40" t="n">
+        <v>37.05331039428711</v>
+      </c>
+      <c r="T40" t="n">
+        <v>29.5123176574707</v>
+      </c>
+      <c r="U40" t="n">
+        <v>23.52684020996094</v>
+      </c>
+      <c r="V40" t="n">
+        <v>19.82741928100586</v>
+      </c>
+      <c r="W40" t="n">
+        <v>16.68377113342285</v>
+      </c>
+      <c r="X40" t="n">
+        <v>16.96085548400879</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>12.27839660644531</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>11.00604248046875</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>9.672407150268555</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>10.03125476837158</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>10.79092788696289</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>person 28</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>harshit_1.ogg</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>dataset\person 28\harshit_1.ogg</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>-246.2100982666016</v>
+      </c>
+      <c r="E41" t="n">
+        <v>124.9230499267578</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-10.17072677612305</v>
+      </c>
+      <c r="G41" t="n">
+        <v>42.8636474609375</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-17.53393173217773</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-24.15909767150879</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-5.306496143341064</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-23.95787811279297</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-7.065333366394043</v>
+      </c>
+      <c r="M41" t="n">
+        <v>-12.57727146148682</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-8.696045875549316</v>
+      </c>
+      <c r="O41" t="n">
+        <v>-8.425534248352051</v>
+      </c>
+      <c r="P41" t="n">
+        <v>-12.90509986877441</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>82.46274566650391</v>
+      </c>
+      <c r="R41" t="n">
+        <v>49.78484344482422</v>
+      </c>
+      <c r="S41" t="n">
+        <v>46.61606216430664</v>
+      </c>
+      <c r="T41" t="n">
+        <v>32.81063461303711</v>
+      </c>
+      <c r="U41" t="n">
+        <v>19.4935474395752</v>
+      </c>
+      <c r="V41" t="n">
+        <v>20.1060905456543</v>
+      </c>
+      <c r="W41" t="n">
+        <v>12.89778423309326</v>
+      </c>
+      <c r="X41" t="n">
+        <v>14.03296089172363</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>12.63073921203613</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>10.11426162719727</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>9.093876838684082</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>10.56334018707275</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>8.584248542785645</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>person 28</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>harshit_2.ogg</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>dataset\person 28\harshit_2.ogg</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>-240.2501525878906</v>
+      </c>
+      <c r="E42" t="n">
+        <v>141.6210479736328</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-14.61767959594727</v>
+      </c>
+      <c r="G42" t="n">
+        <v>33.91931533813477</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-25.82289886474609</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-19.56251907348633</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-5.22670841217041</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-26.83188438415527</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-3.342941045761108</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-15.91719532012939</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-11.54124736785889</v>
+      </c>
+      <c r="O42" t="n">
+        <v>-4.586422920227051</v>
+      </c>
+      <c r="P42" t="n">
+        <v>-14.41274833679199</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>81.41900634765625</v>
+      </c>
+      <c r="R42" t="n">
+        <v>43.07238388061523</v>
+      </c>
+      <c r="S42" t="n">
+        <v>42.25957107543945</v>
+      </c>
+      <c r="T42" t="n">
+        <v>32.46212768554688</v>
+      </c>
+      <c r="U42" t="n">
+        <v>19.00067138671875</v>
+      </c>
+      <c r="V42" t="n">
+        <v>18.92352676391602</v>
+      </c>
+      <c r="W42" t="n">
+        <v>14.37093257904053</v>
+      </c>
+      <c r="X42" t="n">
+        <v>13.54802513122559</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>10.99239253997803</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>11.69825458526611</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>9.7669677734375</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>11.69769954681396</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>8.591986656188965</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>person 28</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>harshit_4.ogg</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>dataset\person 28\harshit_4.ogg</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>-224.4232482910156</v>
+      </c>
+      <c r="E43" t="n">
+        <v>121.6645660400391</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-28.78137397766113</v>
+      </c>
+      <c r="G43" t="n">
+        <v>51.48226928710938</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-7.783470153808594</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-23.53681182861328</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-8.446748733520508</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-20.22367858886719</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-17.102783203125</v>
+      </c>
+      <c r="M43" t="n">
+        <v>-9.636625289916992</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-8.353759765625</v>
+      </c>
+      <c r="O43" t="n">
+        <v>-14.28031063079834</v>
+      </c>
+      <c r="P43" t="n">
+        <v>-11.40643119812012</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>83.22185516357422</v>
+      </c>
+      <c r="R43" t="n">
+        <v>47.01251983642578</v>
+      </c>
+      <c r="S43" t="n">
+        <v>45.70156860351562</v>
+      </c>
+      <c r="T43" t="n">
+        <v>37.04207229614258</v>
+      </c>
+      <c r="U43" t="n">
+        <v>19.09646987915039</v>
+      </c>
+      <c r="V43" t="n">
+        <v>19.20255279541016</v>
+      </c>
+      <c r="W43" t="n">
+        <v>13.46044731140137</v>
+      </c>
+      <c r="X43" t="n">
+        <v>12.62337589263916</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>12.35066318511963</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>11.81838607788086</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>9.154329299926758</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>10.3128719329834</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>8.246455192565918</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>person 29</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>kapil_1.ogg</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>dataset\person 29\kapil_1.ogg</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>-324.3801879882812</v>
+      </c>
+      <c r="E44" t="n">
+        <v>135.1546783447266</v>
+      </c>
+      <c r="F44" t="n">
+        <v>20.70054054260254</v>
+      </c>
+      <c r="G44" t="n">
+        <v>29.74237251281738</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2.023202419281006</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-20.26179695129395</v>
+      </c>
+      <c r="J44" t="n">
+        <v>-8.790897369384766</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-4.78795051574707</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-16.23240280151367</v>
+      </c>
+      <c r="M44" t="n">
+        <v>-7.499528408050537</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-10.34810352325439</v>
+      </c>
+      <c r="O44" t="n">
+        <v>-7.584862232208252</v>
+      </c>
+      <c r="P44" t="n">
+        <v>-10.31723213195801</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>78.38920593261719</v>
+      </c>
+      <c r="R44" t="n">
+        <v>48.95500183105469</v>
+      </c>
+      <c r="S44" t="n">
+        <v>35.48441314697266</v>
+      </c>
+      <c r="T44" t="n">
+        <v>28.69630432128906</v>
+      </c>
+      <c r="U44" t="n">
+        <v>16.85394096374512</v>
+      </c>
+      <c r="V44" t="n">
+        <v>19.04115676879883</v>
+      </c>
+      <c r="W44" t="n">
+        <v>14.45364570617676</v>
+      </c>
+      <c r="X44" t="n">
+        <v>12.50160980224609</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>12.49113464355469</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>10.80944442749023</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>8.614227294921875</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>7.987222671508789</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>7.675607204437256</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>person 29</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>kapil_2.ogg</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>dataset\person 29\kapil_2.ogg</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>-297.9377746582031</v>
+      </c>
+      <c r="E45" t="n">
+        <v>131.0434722900391</v>
+      </c>
+      <c r="F45" t="n">
+        <v>14.02688884735107</v>
+      </c>
+      <c r="G45" t="n">
+        <v>33.33039855957031</v>
+      </c>
+      <c r="H45" t="n">
+        <v>13.40726566314697</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-16.49570465087891</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-22.20087432861328</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3.190672397613525</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-12.67134380340576</v>
+      </c>
+      <c r="M45" t="n">
+        <v>-14.08475303649902</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-12.23516082763672</v>
+      </c>
+      <c r="O45" t="n">
+        <v>-5.541978359222412</v>
+      </c>
+      <c r="P45" t="n">
+        <v>-10.40651226043701</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>77.55065155029297</v>
+      </c>
+      <c r="R45" t="n">
+        <v>56.00645446777344</v>
+      </c>
+      <c r="S45" t="n">
+        <v>38.48147201538086</v>
+      </c>
+      <c r="T45" t="n">
+        <v>27.58687400817871</v>
+      </c>
+      <c r="U45" t="n">
+        <v>17.57201957702637</v>
+      </c>
+      <c r="V45" t="n">
+        <v>20.32891464233398</v>
+      </c>
+      <c r="W45" t="n">
+        <v>18.28652763366699</v>
+      </c>
+      <c r="X45" t="n">
+        <v>15.00673198699951</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>13.3965311050415</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>11.94925498962402</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>8.162168502807617</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>8.390535354614258</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>7.38011360168457</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>person 3</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Kakul_1.ogg</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>dataset\person 3\Kakul_1.ogg</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>-190.283447265625</v>
+      </c>
+      <c r="E46" t="n">
+        <v>133.6089477539062</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.115150809288025</v>
+      </c>
+      <c r="G46" t="n">
+        <v>23.2911205291748</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-24.16946411132812</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-7.406147956848145</v>
+      </c>
+      <c r="J46" t="n">
+        <v>10.43996715545654</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-4.800053119659424</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-7.63574743270874</v>
+      </c>
+      <c r="M46" t="n">
+        <v>-4.589412689208984</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-9.197992324829102</v>
+      </c>
+      <c r="O46" t="n">
+        <v>-8.793667793273926</v>
+      </c>
+      <c r="P46" t="n">
+        <v>-4.535579681396484</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>69.12535095214844</v>
+      </c>
+      <c r="R46" t="n">
+        <v>38.38052368164062</v>
+      </c>
+      <c r="S46" t="n">
+        <v>37.80652236938477</v>
+      </c>
+      <c r="T46" t="n">
+        <v>28.71722984313965</v>
+      </c>
+      <c r="U46" t="n">
+        <v>29.38401985168457</v>
+      </c>
+      <c r="V46" t="n">
+        <v>14.92785263061523</v>
+      </c>
+      <c r="W46" t="n">
+        <v>14.13958549499512</v>
+      </c>
+      <c r="X46" t="n">
+        <v>13.47562980651855</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>11.11625480651855</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>9.429997444152832</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>10.36452198028564</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>11.37071514129639</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>8.672822952270508</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>person 3</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Kakul_2.ogg</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>dataset\person 3\Kakul_2.ogg</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>-196.8373107910156</v>
+      </c>
+      <c r="E47" t="n">
+        <v>137.0163269042969</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.076949834823608</v>
+      </c>
+      <c r="G47" t="n">
+        <v>20.15438652038574</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-21.95147705078125</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-8.13453197479248</v>
+      </c>
+      <c r="J47" t="n">
+        <v>6.260873794555664</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-0.4583200514316559</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-4.726004123687744</v>
+      </c>
+      <c r="M47" t="n">
+        <v>-4.308567047119141</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-7.253196239471436</v>
+      </c>
+      <c r="O47" t="n">
+        <v>-8.211158752441406</v>
+      </c>
+      <c r="P47" t="n">
+        <v>-3.96330714225769</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>73.58183288574219</v>
+      </c>
+      <c r="R47" t="n">
+        <v>37.73896026611328</v>
+      </c>
+      <c r="S47" t="n">
+        <v>35.31673431396484</v>
+      </c>
+      <c r="T47" t="n">
+        <v>27.05937767028809</v>
+      </c>
+      <c r="U47" t="n">
+        <v>31.29484367370605</v>
+      </c>
+      <c r="V47" t="n">
+        <v>17.05021667480469</v>
+      </c>
+      <c r="W47" t="n">
+        <v>11.80955696105957</v>
+      </c>
+      <c r="X47" t="n">
+        <v>12.16705322265625</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>11.09018230438232</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>7.937170028686523</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>9.534924507141113</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>10.3552417755127</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>8.619464874267578</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>person 30</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>anisha_1.ogg</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>dataset\person 30\anisha_1.ogg</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>-465.6536560058594</v>
+      </c>
+      <c r="E48" t="n">
+        <v>112.6094207763672</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21.54707527160645</v>
+      </c>
+      <c r="G48" t="n">
+        <v>30.21061897277832</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-7.069847583770752</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-12.66329288482666</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-5.940185070037842</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-4.825852394104004</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-10.96705532073975</v>
+      </c>
+      <c r="M48" t="n">
+        <v>-6.818028926849365</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-15.38286972045898</v>
+      </c>
+      <c r="O48" t="n">
+        <v>-3.258966684341431</v>
+      </c>
+      <c r="P48" t="n">
+        <v>-9.163272857666016</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>58.79505157470703</v>
+      </c>
+      <c r="R48" t="n">
+        <v>45.62743377685547</v>
+      </c>
+      <c r="S48" t="n">
+        <v>26.96324729919434</v>
+      </c>
+      <c r="T48" t="n">
+        <v>32.30001831054688</v>
+      </c>
+      <c r="U48" t="n">
+        <v>23.15465545654297</v>
+      </c>
+      <c r="V48" t="n">
+        <v>15.72400856018066</v>
+      </c>
+      <c r="W48" t="n">
+        <v>12.97965717315674</v>
+      </c>
+      <c r="X48" t="n">
+        <v>13.87836647033691</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>11.70729446411133</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>8.521382331848145</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>10.41483879089355</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>8.746341705322266</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>9.357212066650391</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>person 30</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>anisha_2.ogg</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>dataset\person 30\anisha_2.ogg</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>-484.6829223632812</v>
+      </c>
+      <c r="E49" t="n">
+        <v>116.2566375732422</v>
+      </c>
+      <c r="F49" t="n">
+        <v>39.12118911743164</v>
+      </c>
+      <c r="G49" t="n">
+        <v>30.06397247314453</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-22.70480918884277</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-4.837339401245117</v>
+      </c>
+      <c r="J49" t="n">
+        <v>-16.28741645812988</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-5.159249305725098</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-8.211940765380859</v>
+      </c>
+      <c r="M49" t="n">
+        <v>-16.56889533996582</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-2.069540739059448</v>
+      </c>
+      <c r="O49" t="n">
+        <v>-8.675417900085449</v>
+      </c>
+      <c r="P49" t="n">
+        <v>-12.00079822540283</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>60.73855590820312</v>
+      </c>
+      <c r="R49" t="n">
+        <v>47.41333389282227</v>
+      </c>
+      <c r="S49" t="n">
+        <v>28.80617332458496</v>
+      </c>
+      <c r="T49" t="n">
+        <v>27.82364463806152</v>
+      </c>
+      <c r="U49" t="n">
+        <v>28.18973350524902</v>
+      </c>
+      <c r="V49" t="n">
+        <v>16.45576286315918</v>
+      </c>
+      <c r="W49" t="n">
+        <v>17.94898986816406</v>
+      </c>
+      <c r="X49" t="n">
+        <v>12.72195148468018</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>11.24168109893799</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>10.51891231536865</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>8.329865455627441</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>9.170406341552734</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>9.342425346374512</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>person 31</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>uchist_1.ogg</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>dataset\person 31\uchist_1.ogg</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>-308.1812133789062</v>
+      </c>
+      <c r="E50" t="n">
+        <v>114.7631301879883</v>
+      </c>
+      <c r="F50" t="n">
+        <v>27.42999267578125</v>
+      </c>
+      <c r="G50" t="n">
+        <v>30.85193061828613</v>
+      </c>
+      <c r="H50" t="n">
+        <v>12.58181476593018</v>
+      </c>
+      <c r="I50" t="n">
+        <v>9.333892822265625</v>
+      </c>
+      <c r="J50" t="n">
+        <v>-11.05212116241455</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-16.1427059173584</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-6.43009614944458</v>
+      </c>
+      <c r="M50" t="n">
+        <v>-6.335826396942139</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-9.943606376647949</v>
+      </c>
+      <c r="O50" t="n">
+        <v>-3.692275285720825</v>
+      </c>
+      <c r="P50" t="n">
+        <v>-7.446938991546631</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>85.44676208496094</v>
+      </c>
+      <c r="R50" t="n">
+        <v>52.61627960205078</v>
+      </c>
+      <c r="S50" t="n">
+        <v>41.81206512451172</v>
+      </c>
+      <c r="T50" t="n">
+        <v>34.21482086181641</v>
+      </c>
+      <c r="U50" t="n">
+        <v>22.85800933837891</v>
+      </c>
+      <c r="V50" t="n">
+        <v>14.10485363006592</v>
+      </c>
+      <c r="W50" t="n">
+        <v>13.81807422637939</v>
+      </c>
+      <c r="X50" t="n">
+        <v>18.09701538085938</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>11.66872787475586</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>11.70572757720947</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>8.967845916748047</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>7.266478061676025</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>8.680811882019043</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>person 31</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>uchist_2.ogg</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>dataset\person 31\uchist_2.ogg</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>-316.845947265625</v>
+      </c>
+      <c r="E51" t="n">
+        <v>123.6270751953125</v>
+      </c>
+      <c r="F51" t="n">
+        <v>27.75157928466797</v>
+      </c>
+      <c r="G51" t="n">
+        <v>33.27535629272461</v>
+      </c>
+      <c r="H51" t="n">
+        <v>10.72974967956543</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-4.080448150634766</v>
+      </c>
+      <c r="J51" t="n">
+        <v>-17.42192077636719</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-10.86059856414795</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-7.9779052734375</v>
+      </c>
+      <c r="M51" t="n">
+        <v>-6.545088291168213</v>
+      </c>
+      <c r="N51" t="n">
+        <v>-11.55636501312256</v>
+      </c>
+      <c r="O51" t="n">
+        <v>-0.6609389185905457</v>
+      </c>
+      <c r="P51" t="n">
+        <v>-5.037771224975586</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>64.953125</v>
+      </c>
+      <c r="R51" t="n">
+        <v>52.46412658691406</v>
+      </c>
+      <c r="S51" t="n">
+        <v>36.62564468383789</v>
+      </c>
+      <c r="T51" t="n">
+        <v>30.26807975769043</v>
+      </c>
+      <c r="U51" t="n">
+        <v>22.21001052856445</v>
+      </c>
+      <c r="V51" t="n">
+        <v>18.22575378417969</v>
+      </c>
+      <c r="W51" t="n">
+        <v>15.02075290679932</v>
+      </c>
+      <c r="X51" t="n">
+        <v>19.27973365783691</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>11.39815902709961</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>12.38002109527588</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>9.641401290893555</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>8.149274826049805</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>8.491599082946777</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>person 32</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>yug_1.ogg</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>dataset\person 32\yug_1.ogg</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>-214.5449676513672</v>
+      </c>
+      <c r="E52" t="n">
+        <v>137.6085052490234</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-57.97356033325195</v>
+      </c>
+      <c r="G52" t="n">
+        <v>60.52235412597656</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4.041022300720215</v>
+      </c>
+      <c r="I52" t="n">
+        <v>-17.6016674041748</v>
+      </c>
+      <c r="J52" t="n">
+        <v>-7.901891231536865</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-13.09739398956299</v>
+      </c>
+      <c r="L52" t="n">
+        <v>-18.96970748901367</v>
+      </c>
+      <c r="M52" t="n">
+        <v>-16.03158187866211</v>
+      </c>
+      <c r="N52" t="n">
+        <v>-9.486040115356445</v>
+      </c>
+      <c r="O52" t="n">
+        <v>-18.20236015319824</v>
+      </c>
+      <c r="P52" t="n">
+        <v>-7.748525142669678</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>84.45383453369141</v>
+      </c>
+      <c r="R52" t="n">
+        <v>47.51968765258789</v>
+      </c>
+      <c r="S52" t="n">
+        <v>43.48736953735352</v>
+      </c>
+      <c r="T52" t="n">
+        <v>34.34400177001953</v>
+      </c>
+      <c r="U52" t="n">
+        <v>21.82061767578125</v>
+      </c>
+      <c r="V52" t="n">
+        <v>22.18248748779297</v>
+      </c>
+      <c r="W52" t="n">
+        <v>20.75617408752441</v>
+      </c>
+      <c r="X52" t="n">
+        <v>17.20969009399414</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>16.61060333251953</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>13.02517890930176</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>11.41374206542969</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>10.11754512786865</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>9.898459434509277</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>person 32</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>yug_2.ogg</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>dataset\person 32\yug_2.ogg</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>-187.7301330566406</v>
+      </c>
+      <c r="E53" t="n">
+        <v>144.1079711914062</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-80.31039428710938</v>
+      </c>
+      <c r="G53" t="n">
+        <v>63.33536529541016</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-3.069978713989258</v>
+      </c>
+      <c r="I53" t="n">
+        <v>-19.61112594604492</v>
+      </c>
+      <c r="J53" t="n">
+        <v>-5.109501361846924</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-14.70250797271729</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-14.58237361907959</v>
+      </c>
+      <c r="M53" t="n">
+        <v>-15.20962524414062</v>
+      </c>
+      <c r="N53" t="n">
+        <v>-8.233778953552246</v>
+      </c>
+      <c r="O53" t="n">
+        <v>-17.56955528259277</v>
+      </c>
+      <c r="P53" t="n">
+        <v>-7.368851661682129</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>67.30784606933594</v>
+      </c>
+      <c r="R53" t="n">
+        <v>40.2510986328125</v>
+      </c>
+      <c r="S53" t="n">
+        <v>42.615966796875</v>
+      </c>
+      <c r="T53" t="n">
+        <v>30.82370376586914</v>
+      </c>
+      <c r="U53" t="n">
+        <v>19.75558280944824</v>
+      </c>
+      <c r="V53" t="n">
+        <v>19.80203628540039</v>
+      </c>
+      <c r="W53" t="n">
+        <v>18.75736999511719</v>
+      </c>
+      <c r="X53" t="n">
+        <v>15.82434368133545</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>13.78455066680908</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>11.00095748901367</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>9.761628150939941</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>9.736648559570312</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>9.415058135986328</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>person 33</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>kushal_1.ogg</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>dataset\person 33\kushal_1.ogg</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>-353.7056884765625</v>
+      </c>
+      <c r="E54" t="n">
+        <v>138.9226379394531</v>
+      </c>
+      <c r="F54" t="n">
+        <v>31.27920150756836</v>
+      </c>
+      <c r="G54" t="n">
+        <v>6.245642185211182</v>
+      </c>
+      <c r="H54" t="n">
+        <v>7.791232109069824</v>
+      </c>
+      <c r="I54" t="n">
+        <v>3.858528614044189</v>
+      </c>
+      <c r="J54" t="n">
+        <v>-15.67633628845215</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-16.23328971862793</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-5.908332347869873</v>
+      </c>
+      <c r="M54" t="n">
+        <v>-13.81318283081055</v>
+      </c>
+      <c r="N54" t="n">
+        <v>-4.738839626312256</v>
+      </c>
+      <c r="O54" t="n">
+        <v>-7.72522497177124</v>
+      </c>
+      <c r="P54" t="n">
+        <v>-8.855106353759766</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>90.06693267822266</v>
+      </c>
+      <c r="R54" t="n">
+        <v>56.27338027954102</v>
+      </c>
+      <c r="S54" t="n">
+        <v>33.56408309936523</v>
+      </c>
+      <c r="T54" t="n">
+        <v>24.5563793182373</v>
+      </c>
+      <c r="U54" t="n">
+        <v>18.11230278015137</v>
+      </c>
+      <c r="V54" t="n">
+        <v>14.70199012756348</v>
+      </c>
+      <c r="W54" t="n">
+        <v>18.9300537109375</v>
+      </c>
+      <c r="X54" t="n">
+        <v>15.86143684387207</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>12.17967700958252</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>13.02080059051514</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>10.03925323486328</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>8.778785705566406</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>10.37950229644775</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>person 33</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>kushal_2.ogg</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>dataset\person 33\kushal_2.ogg</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>-281.5736389160156</v>
+      </c>
+      <c r="E55" t="n">
+        <v>127.2256240844727</v>
+      </c>
+      <c r="F55" t="n">
+        <v>33.48838806152344</v>
+      </c>
+      <c r="G55" t="n">
+        <v>26.10984230041504</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-5.929999351501465</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-2.151679992675781</v>
+      </c>
+      <c r="J55" t="n">
+        <v>-15.64864826202393</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-18.20459747314453</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-6.288395404815674</v>
+      </c>
+      <c r="M55" t="n">
+        <v>-17.58111000061035</v>
+      </c>
+      <c r="N55" t="n">
+        <v>-5.04248046875</v>
+      </c>
+      <c r="O55" t="n">
+        <v>-10.13194465637207</v>
+      </c>
+      <c r="P55" t="n">
+        <v>-14.72093486785889</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>102.1594161987305</v>
+      </c>
+      <c r="R55" t="n">
+        <v>60.39371871948242</v>
+      </c>
+      <c r="S55" t="n">
+        <v>35.05391311645508</v>
+      </c>
+      <c r="T55" t="n">
+        <v>28.17009925842285</v>
+      </c>
+      <c r="U55" t="n">
+        <v>17.44703483581543</v>
+      </c>
+      <c r="V55" t="n">
+        <v>17.66764259338379</v>
+      </c>
+      <c r="W55" t="n">
+        <v>18.1828441619873</v>
+      </c>
+      <c r="X55" t="n">
+        <v>15.47097969055176</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>13.24603748321533</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>13.61801910400391</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>9.552223205566406</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>10.3119649887085</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>11.5520658493042</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>person 34</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>aryan_1.ogg</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>dataset\person 34\aryan_1.ogg</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>-277.4549255371094</v>
+      </c>
+      <c r="E56" t="n">
+        <v>114.521125793457</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-16.76680946350098</v>
+      </c>
+      <c r="G56" t="n">
+        <v>40.09193801879883</v>
+      </c>
+      <c r="H56" t="n">
+        <v>2.700610876083374</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-36.04873275756836</v>
+      </c>
+      <c r="J56" t="n">
+        <v>-21.99965286254883</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-9.699584007263184</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-14.22228622436523</v>
+      </c>
+      <c r="M56" t="n">
+        <v>-12.69406032562256</v>
+      </c>
+      <c r="N56" t="n">
+        <v>-10.30362319946289</v>
+      </c>
+      <c r="O56" t="n">
+        <v>-6.292177200317383</v>
+      </c>
+      <c r="P56" t="n">
+        <v>-4.977135181427002</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>98.65097045898438</v>
+      </c>
+      <c r="R56" t="n">
+        <v>52.22968292236328</v>
+      </c>
+      <c r="S56" t="n">
+        <v>43.92961502075195</v>
+      </c>
+      <c r="T56" t="n">
+        <v>34.49890899658203</v>
+      </c>
+      <c r="U56" t="n">
+        <v>21.65865135192871</v>
+      </c>
+      <c r="V56" t="n">
+        <v>20.55267333984375</v>
+      </c>
+      <c r="W56" t="n">
+        <v>17.37928199768066</v>
+      </c>
+      <c r="X56" t="n">
+        <v>16.65326881408691</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>11.74692058563232</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>11.78106784820557</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>10.01436901092529</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>9.817768096923828</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>9.844478607177734</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>person 34</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>aryan_2.ogg</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>dataset\person 34\aryan_2.ogg</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>-278.8909301757812</v>
+      </c>
+      <c r="E57" t="n">
+        <v>111.8300018310547</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-15.40710544586182</v>
+      </c>
+      <c r="G57" t="n">
+        <v>38.95182037353516</v>
+      </c>
+      <c r="H57" t="n">
+        <v>5.76634407043457</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-36.18192291259766</v>
+      </c>
+      <c r="J57" t="n">
+        <v>-21.8931941986084</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-8.704999923706055</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-17.28514289855957</v>
+      </c>
+      <c r="M57" t="n">
+        <v>-10.64297866821289</v>
+      </c>
+      <c r="N57" t="n">
+        <v>-9.473019599914551</v>
+      </c>
+      <c r="O57" t="n">
+        <v>-7.773548126220703</v>
+      </c>
+      <c r="P57" t="n">
+        <v>-6.20173168182373</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>104.9056015014648</v>
+      </c>
+      <c r="R57" t="n">
+        <v>49.26176834106445</v>
+      </c>
+      <c r="S57" t="n">
+        <v>42.33060455322266</v>
+      </c>
+      <c r="T57" t="n">
+        <v>36.20293426513672</v>
+      </c>
+      <c r="U57" t="n">
+        <v>21.44687271118164</v>
+      </c>
+      <c r="V57" t="n">
+        <v>21.1485595703125</v>
+      </c>
+      <c r="W57" t="n">
+        <v>16.52013206481934</v>
+      </c>
+      <c r="X57" t="n">
+        <v>15.3092212677002</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>12.6143741607666</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>11.88924884796143</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>9.762723922729492</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>8.419194221496582</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>8.929122924804688</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>person 35</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>mohit_1.ogg</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>dataset\person 35\mohit_1.ogg</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>-444.6673889160156</v>
+      </c>
+      <c r="E58" t="n">
+        <v>124.1644515991211</v>
+      </c>
+      <c r="F58" t="n">
+        <v>23.16630554199219</v>
+      </c>
+      <c r="G58" t="n">
+        <v>19.13892364501953</v>
+      </c>
+      <c r="H58" t="n">
+        <v>15.42267322540283</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-2.770617485046387</v>
+      </c>
+      <c r="J58" t="n">
+        <v>-4.471717357635498</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-8.144162178039551</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-7.768331527709961</v>
+      </c>
+      <c r="M58" t="n">
+        <v>-4.162942886352539</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.05628377944231033</v>
+      </c>
+      <c r="O58" t="n">
+        <v>-5.969676494598389</v>
+      </c>
+      <c r="P58" t="n">
+        <v>-10.27068424224854</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>110.115234375</v>
+      </c>
+      <c r="R58" t="n">
+        <v>54.53167724609375</v>
+      </c>
+      <c r="S58" t="n">
+        <v>38.61249923706055</v>
+      </c>
+      <c r="T58" t="n">
+        <v>32.05418014526367</v>
+      </c>
+      <c r="U58" t="n">
+        <v>17.24824142456055</v>
+      </c>
+      <c r="V58" t="n">
+        <v>22.24419975280762</v>
+      </c>
+      <c r="W58" t="n">
+        <v>16.04420280456543</v>
+      </c>
+      <c r="X58" t="n">
+        <v>13.85482025146484</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>10.92047500610352</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>13.2835693359375</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>9.79121208190918</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>9.452803611755371</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>9.049367904663086</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>person 35</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>mohit_2.ogg</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>dataset\person 35\mohit_2.ogg</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>-423.5763854980469</v>
+      </c>
+      <c r="E59" t="n">
+        <v>131.5092926025391</v>
+      </c>
+      <c r="F59" t="n">
+        <v>33.57487869262695</v>
+      </c>
+      <c r="G59" t="n">
+        <v>16.85190582275391</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.994786620140076</v>
+      </c>
+      <c r="I59" t="n">
+        <v>10.54657649993896</v>
+      </c>
+      <c r="J59" t="n">
+        <v>-10.78670692443848</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-17.44351768493652</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-6.136281967163086</v>
+      </c>
+      <c r="M59" t="n">
+        <v>-4.733487129211426</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.2738951444625854</v>
+      </c>
+      <c r="O59" t="n">
+        <v>-6.692953586578369</v>
+      </c>
+      <c r="P59" t="n">
+        <v>-9.422252655029297</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>104.5602569580078</v>
+      </c>
+      <c r="R59" t="n">
+        <v>54.70085144042969</v>
+      </c>
+      <c r="S59" t="n">
+        <v>29.98511123657227</v>
+      </c>
+      <c r="T59" t="n">
+        <v>31.09702682495117</v>
+      </c>
+      <c r="U59" t="n">
+        <v>18.70390129089355</v>
+      </c>
+      <c r="V59" t="n">
+        <v>16.64605331420898</v>
+      </c>
+      <c r="W59" t="n">
+        <v>18.42476272583008</v>
+      </c>
+      <c r="X59" t="n">
+        <v>15.268385887146</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>11.7458963394165</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>15.08718109130859</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>9.618152618408203</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>9.09449291229248</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>9.853418350219727</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>person 35</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>mohit_3.ogg</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>dataset\person 35\mohit_3.ogg</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>-415.0833740234375</v>
+      </c>
+      <c r="E60" t="n">
+        <v>121.8332977294922</v>
+      </c>
+      <c r="F60" t="n">
+        <v>39.62260437011719</v>
+      </c>
+      <c r="G60" t="n">
+        <v>16.78773498535156</v>
+      </c>
+      <c r="H60" t="n">
+        <v>6.933207035064697</v>
+      </c>
+      <c r="I60" t="n">
+        <v>5.022029399871826</v>
+      </c>
+      <c r="J60" t="n">
+        <v>-11.8987979888916</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-10.38849925994873</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-8.749146461486816</v>
+      </c>
+      <c r="M60" t="n">
+        <v>-9.653755187988281</v>
+      </c>
+      <c r="N60" t="n">
+        <v>1.438817620277405</v>
+      </c>
+      <c r="O60" t="n">
+        <v>-4.908359527587891</v>
+      </c>
+      <c r="P60" t="n">
+        <v>-12.72043037414551</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>97.24942016601562</v>
+      </c>
+      <c r="R60" t="n">
+        <v>59.89488220214844</v>
+      </c>
+      <c r="S60" t="n">
+        <v>37.51870346069336</v>
+      </c>
+      <c r="T60" t="n">
+        <v>32.55846786499023</v>
+      </c>
+      <c r="U60" t="n">
+        <v>18.3155460357666</v>
+      </c>
+      <c r="V60" t="n">
+        <v>19.58695983886719</v>
+      </c>
+      <c r="W60" t="n">
+        <v>20.77068710327148</v>
+      </c>
+      <c r="X60" t="n">
+        <v>12.91335868835449</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>10.58409404754639</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>13.41504859924316</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>9.538527488708496</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>9.815642356872559</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>10.5024995803833</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>person 35</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>mohit_4.ogg</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>dataset\person 35\mohit_4.ogg</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>-386.224853515625</v>
+      </c>
+      <c r="E61" t="n">
+        <v>130.4182434082031</v>
+      </c>
+      <c r="F61" t="n">
+        <v>21.61054801940918</v>
+      </c>
+      <c r="G61" t="n">
+        <v>30.85459327697754</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1.751876592636108</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-0.4203822612762451</v>
+      </c>
+      <c r="J61" t="n">
+        <v>-9.465001106262207</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-20.47898292541504</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-8.063581466674805</v>
+      </c>
+      <c r="M61" t="n">
+        <v>-4.198132991790771</v>
+      </c>
+      <c r="N61" t="n">
+        <v>-3.408721208572388</v>
+      </c>
+      <c r="O61" t="n">
+        <v>-4.624478816986084</v>
+      </c>
+      <c r="P61" t="n">
+        <v>-11.05064582824707</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>92.65379333496094</v>
+      </c>
+      <c r="R61" t="n">
+        <v>60.90190124511719</v>
+      </c>
+      <c r="S61" t="n">
+        <v>36.41575241088867</v>
+      </c>
+      <c r="T61" t="n">
+        <v>35.52265548706055</v>
+      </c>
+      <c r="U61" t="n">
+        <v>21.02906799316406</v>
+      </c>
+      <c r="V61" t="n">
+        <v>20.28528022766113</v>
+      </c>
+      <c r="W61" t="n">
+        <v>20.10711479187012</v>
+      </c>
+      <c r="X61" t="n">
+        <v>15.59069728851318</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>14.43491554260254</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>14.68626403808594</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>10.80429840087891</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>10.8916072845459</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>10.77245330810547</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>person 36</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>om_!.ogg</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>dataset\person 36\om_!.ogg</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>-254.7970428466797</v>
+      </c>
+      <c r="E62" t="n">
+        <v>125.5931549072266</v>
+      </c>
+      <c r="F62" t="n">
+        <v>27.2747859954834</v>
+      </c>
+      <c r="G62" t="n">
+        <v>19.31343269348145</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-15.60981941223145</v>
+      </c>
+      <c r="I62" t="n">
+        <v>-10.0490083694458</v>
+      </c>
+      <c r="J62" t="n">
+        <v>-16.97013092041016</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-14.92357730865479</v>
+      </c>
+      <c r="L62" t="n">
+        <v>-2.68035364151001</v>
+      </c>
+      <c r="M62" t="n">
+        <v>-29.41190910339355</v>
+      </c>
+      <c r="N62" t="n">
+        <v>-3.437254190444946</v>
+      </c>
+      <c r="O62" t="n">
+        <v>-4.776679039001465</v>
+      </c>
+      <c r="P62" t="n">
+        <v>-12.36459445953369</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>89.67417144775391</v>
+      </c>
+      <c r="R62" t="n">
+        <v>62.47548675537109</v>
+      </c>
+      <c r="S62" t="n">
+        <v>32.00107955932617</v>
+      </c>
+      <c r="T62" t="n">
+        <v>43.05760955810547</v>
+      </c>
+      <c r="U62" t="n">
+        <v>22.00748252868652</v>
+      </c>
+      <c r="V62" t="n">
+        <v>21.07443809509277</v>
+      </c>
+      <c r="W62" t="n">
+        <v>18.17378234863281</v>
+      </c>
+      <c r="X62" t="n">
+        <v>14.74174118041992</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>15.10261917114258</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>17.39238929748535</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>11.28926277160645</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>9.96770191192627</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>10.51453018188477</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>person 36</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>om_2.ogg</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>dataset\person 36\om_2.ogg</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>-235.7554321289062</v>
+      </c>
+      <c r="E63" t="n">
+        <v>139.2917938232422</v>
+      </c>
+      <c r="F63" t="n">
+        <v>13.454833984375</v>
+      </c>
+      <c r="G63" t="n">
+        <v>34.34274673461914</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-15.77021026611328</v>
+      </c>
+      <c r="I63" t="n">
+        <v>-16.48377227783203</v>
+      </c>
+      <c r="J63" t="n">
+        <v>-17.4273624420166</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-20.14789962768555</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-4.673211574554443</v>
+      </c>
+      <c r="M63" t="n">
+        <v>-25.59561538696289</v>
+      </c>
+      <c r="N63" t="n">
+        <v>-9.637410163879395</v>
+      </c>
+      <c r="O63" t="n">
+        <v>-4.122169971466064</v>
+      </c>
+      <c r="P63" t="n">
+        <v>-12.93187713623047</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>81.82145690917969</v>
+      </c>
+      <c r="R63" t="n">
+        <v>54.12909698486328</v>
+      </c>
+      <c r="S63" t="n">
+        <v>33.99483108520508</v>
+      </c>
+      <c r="T63" t="n">
+        <v>40.56527709960938</v>
+      </c>
+      <c r="U63" t="n">
+        <v>20.3157844543457</v>
+      </c>
+      <c r="V63" t="n">
+        <v>17.86899185180664</v>
+      </c>
+      <c r="W63" t="n">
+        <v>17.71457672119141</v>
+      </c>
+      <c r="X63" t="n">
+        <v>16.14283561706543</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>15.67755031585693</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>17.15423965454102</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>11.63630104064941</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>10.16684436798096</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>9.892553329467773</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>person 37</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>nehal_1.ogg</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>dataset\person 37\nehal_1.ogg</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>-297.3018188476562</v>
+      </c>
+      <c r="E64" t="n">
+        <v>118.9775085449219</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1.200323224067688</v>
+      </c>
+      <c r="G64" t="n">
+        <v>14.86627101898193</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-4.669356346130371</v>
+      </c>
+      <c r="I64" t="n">
+        <v>-14.58564186096191</v>
+      </c>
+      <c r="J64" t="n">
+        <v>-11.74206161499023</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-4.783528327941895</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-18.86002349853516</v>
+      </c>
+      <c r="M64" t="n">
+        <v>-5.50392484664917</v>
+      </c>
+      <c r="N64" t="n">
+        <v>-10.19527816772461</v>
+      </c>
+      <c r="O64" t="n">
+        <v>-6.15611457824707</v>
+      </c>
+      <c r="P64" t="n">
+        <v>-5.847312927246094</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>78.89299774169922</v>
+      </c>
+      <c r="R64" t="n">
+        <v>39.26357650756836</v>
+      </c>
+      <c r="S64" t="n">
+        <v>34.74308013916016</v>
+      </c>
+      <c r="T64" t="n">
+        <v>23.96899032592773</v>
+      </c>
+      <c r="U64" t="n">
+        <v>18.09050369262695</v>
+      </c>
+      <c r="V64" t="n">
+        <v>17.18493270874023</v>
+      </c>
+      <c r="W64" t="n">
+        <v>14.95584869384766</v>
+      </c>
+      <c r="X64" t="n">
+        <v>13.48922061920166</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>13.21902561187744</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>9.01417350769043</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>8.271900177001953</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>7.083547592163086</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>6.501342296600342</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>person 37</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>nehal_2.ogg</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>dataset\person 37\nehal_2.ogg</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>-327.303466796875</v>
+      </c>
+      <c r="E65" t="n">
+        <v>125.5333938598633</v>
+      </c>
+      <c r="F65" t="n">
+        <v>5.583927631378174</v>
+      </c>
+      <c r="G65" t="n">
+        <v>22.03912544250488</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-13.36642646789551</v>
+      </c>
+      <c r="I65" t="n">
+        <v>-6.463416576385498</v>
+      </c>
+      <c r="J65" t="n">
+        <v>-13.92724418640137</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-9.283884048461914</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-14.91791820526123</v>
+      </c>
+      <c r="M65" t="n">
+        <v>-5.072164058685303</v>
+      </c>
+      <c r="N65" t="n">
+        <v>-8.003928184509277</v>
+      </c>
+      <c r="O65" t="n">
+        <v>-7.924027442932129</v>
+      </c>
+      <c r="P65" t="n">
+        <v>-4.870115280151367</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>51.47602081298828</v>
+      </c>
+      <c r="R65" t="n">
+        <v>44.2633171081543</v>
+      </c>
+      <c r="S65" t="n">
+        <v>23.15540313720703</v>
+      </c>
+      <c r="T65" t="n">
+        <v>19.64772033691406</v>
+      </c>
+      <c r="U65" t="n">
+        <v>11.05841255187988</v>
+      </c>
+      <c r="V65" t="n">
+        <v>13.25731945037842</v>
+      </c>
+      <c r="W65" t="n">
+        <v>12.04617500305176</v>
+      </c>
+      <c r="X65" t="n">
+        <v>10.83787155151367</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>9.771706581115723</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>8.688150405883789</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>7.670083522796631</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>6.531048774719238</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>5.584943771362305</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>person 39</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>yashi_1.ogg</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>dataset\person 39\yashi_1.ogg</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>-225.1929473876953</v>
+      </c>
+      <c r="E66" t="n">
+        <v>113.4493789672852</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-22.29241180419922</v>
+      </c>
+      <c r="G66" t="n">
+        <v>30.51932144165039</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-29.64214706420898</v>
+      </c>
+      <c r="I66" t="n">
+        <v>-15.17801284790039</v>
+      </c>
+      <c r="J66" t="n">
+        <v>-9.084718704223633</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-11.15530681610107</v>
+      </c>
+      <c r="L66" t="n">
+        <v>-14.00184631347656</v>
+      </c>
+      <c r="M66" t="n">
+        <v>-16.71494674682617</v>
+      </c>
+      <c r="N66" t="n">
+        <v>-5.639621734619141</v>
+      </c>
+      <c r="O66" t="n">
+        <v>-12.01323127746582</v>
+      </c>
+      <c r="P66" t="n">
+        <v>-2.84876012802124</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>90.93248748779297</v>
+      </c>
+      <c r="R66" t="n">
+        <v>35.23521041870117</v>
+      </c>
+      <c r="S66" t="n">
+        <v>40.48356246948242</v>
+      </c>
+      <c r="T66" t="n">
+        <v>32.90330505371094</v>
+      </c>
+      <c r="U66" t="n">
+        <v>28.98665618896484</v>
+      </c>
+      <c r="V66" t="n">
+        <v>19.41733551025391</v>
+      </c>
+      <c r="W66" t="n">
+        <v>13.90125560760498</v>
+      </c>
+      <c r="X66" t="n">
+        <v>12.86359691619873</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>12.96959018707275</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>9.362946510314941</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>10.88275337219238</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>10.48393821716309</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>10.15488910675049</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>person 39</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>yashi_2.ogg</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>dataset\person 39\yashi_2.ogg</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>-240.3481903076172</v>
+      </c>
+      <c r="E67" t="n">
+        <v>109.3690719604492</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-7.348677158355713</v>
+      </c>
+      <c r="G67" t="n">
+        <v>31.00968360900879</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-24.13865852355957</v>
+      </c>
+      <c r="I67" t="n">
+        <v>-10.42101573944092</v>
+      </c>
+      <c r="J67" t="n">
+        <v>-9.457828521728516</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-14.3804407119751</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-9.941414833068848</v>
+      </c>
+      <c r="M67" t="n">
+        <v>-12.96102142333984</v>
+      </c>
+      <c r="N67" t="n">
+        <v>-5.507748603820801</v>
+      </c>
+      <c r="O67" t="n">
+        <v>-7.472206115722656</v>
+      </c>
+      <c r="P67" t="n">
+        <v>-6.743484497070312</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>100.8925094604492</v>
+      </c>
+      <c r="R67" t="n">
+        <v>35.03450393676758</v>
+      </c>
+      <c r="S67" t="n">
+        <v>39.72949981689453</v>
+      </c>
+      <c r="T67" t="n">
+        <v>34.69679260253906</v>
+      </c>
+      <c r="U67" t="n">
+        <v>28.46064567565918</v>
+      </c>
+      <c r="V67" t="n">
+        <v>17.8825626373291</v>
+      </c>
+      <c r="W67" t="n">
+        <v>13.05806541442871</v>
+      </c>
+      <c r="X67" t="n">
+        <v>13.47843360900879</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>12.48887825012207</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>9.149469375610352</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>10.36937046051025</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>10.04949569702148</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>8.296557426452637</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>person 4</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Priyal_1.ogg</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>dataset\person 4\Priyal_1.ogg</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>-312.5486450195312</v>
+      </c>
+      <c r="E68" t="n">
+        <v>150.1796722412109</v>
+      </c>
+      <c r="F68" t="n">
+        <v>7.713390350341797</v>
+      </c>
+      <c r="G68" t="n">
+        <v>6.145754814147949</v>
+      </c>
+      <c r="H68" t="n">
+        <v>3.052168369293213</v>
+      </c>
+      <c r="I68" t="n">
+        <v>-1.776192665100098</v>
+      </c>
+      <c r="J68" t="n">
+        <v>-9.216532707214355</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-3.588597774505615</v>
+      </c>
+      <c r="L68" t="n">
+        <v>-6.173582077026367</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.8687239289283752</v>
+      </c>
+      <c r="N68" t="n">
+        <v>-0.4865387380123138</v>
+      </c>
+      <c r="O68" t="n">
+        <v>-4.973953723907471</v>
+      </c>
+      <c r="P68" t="n">
+        <v>-10.27382564544678</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>65.61749267578125</v>
+      </c>
+      <c r="R68" t="n">
+        <v>37.27419281005859</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25.96170616149902</v>
+      </c>
+      <c r="T68" t="n">
+        <v>21.23504829406738</v>
+      </c>
+      <c r="U68" t="n">
+        <v>13.79465866088867</v>
+      </c>
+      <c r="V68" t="n">
+        <v>16.28481674194336</v>
+      </c>
+      <c r="W68" t="n">
+        <v>13.23305130004883</v>
+      </c>
+      <c r="X68" t="n">
+        <v>10.71380233764648</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>10.04259204864502</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>7.751870632171631</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>7.407976627349854</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>8.53666877746582</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>8.279526710510254</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>person 4</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Priyal_2.ogg</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>dataset\person 4\Priyal_2.ogg</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>-311.0335998535156</v>
+      </c>
+      <c r="E69" t="n">
+        <v>139.7058715820312</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2.826289176940918</v>
+      </c>
+      <c r="G69" t="n">
+        <v>18.36519813537598</v>
+      </c>
+      <c r="H69" t="n">
+        <v>6.796773433685303</v>
+      </c>
+      <c r="I69" t="n">
+        <v>-1.709654569625854</v>
+      </c>
+      <c r="J69" t="n">
+        <v>-10.10908794403076</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-0.4125159382820129</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.2676233649253845</v>
+      </c>
+      <c r="M69" t="n">
+        <v>-0.4392862021923065</v>
+      </c>
+      <c r="N69" t="n">
+        <v>-2.075055122375488</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.571028470993042</v>
+      </c>
+      <c r="P69" t="n">
+        <v>-6.892978668212891</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>70.24768829345703</v>
+      </c>
+      <c r="R69" t="n">
+        <v>34.07271957397461</v>
+      </c>
+      <c r="S69" t="n">
+        <v>29.20603370666504</v>
+      </c>
+      <c r="T69" t="n">
+        <v>20.54103469848633</v>
+      </c>
+      <c r="U69" t="n">
+        <v>13.63752746582031</v>
+      </c>
+      <c r="V69" t="n">
+        <v>16.40136337280273</v>
+      </c>
+      <c r="W69" t="n">
+        <v>13.55265617370605</v>
+      </c>
+      <c r="X69" t="n">
+        <v>9.749473571777344</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>10.3587532043457</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>7.531620502471924</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>6.957065582275391</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>7.562671184539795</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>7.419523239135742</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>person 5</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Shourya_1.ogg</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>dataset\person 5\Shourya_1.ogg</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>-358.8090515136719</v>
+      </c>
+      <c r="E70" t="n">
+        <v>114.3142395019531</v>
+      </c>
+      <c r="F70" t="n">
+        <v>37.55840682983398</v>
+      </c>
+      <c r="G70" t="n">
+        <v>13.92228031158447</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1.206528663635254</v>
+      </c>
+      <c r="I70" t="n">
+        <v>6.434402942657471</v>
+      </c>
+      <c r="J70" t="n">
+        <v>-8.759699821472168</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.6461262702941895</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-2.814217090606689</v>
+      </c>
+      <c r="M70" t="n">
+        <v>-3.152784109115601</v>
+      </c>
+      <c r="N70" t="n">
+        <v>1.124211668968201</v>
+      </c>
+      <c r="O70" t="n">
+        <v>2.428881645202637</v>
+      </c>
+      <c r="P70" t="n">
+        <v>-3.400106191635132</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>89.46620941162109</v>
+      </c>
+      <c r="R70" t="n">
+        <v>61.67924499511719</v>
+      </c>
+      <c r="S70" t="n">
+        <v>28.91465950012207</v>
+      </c>
+      <c r="T70" t="n">
+        <v>31.10330772399902</v>
+      </c>
+      <c r="U70" t="n">
+        <v>17.80472946166992</v>
+      </c>
+      <c r="V70" t="n">
+        <v>16.71832847595215</v>
+      </c>
+      <c r="W70" t="n">
+        <v>18.56906890869141</v>
+      </c>
+      <c r="X70" t="n">
+        <v>13.13578224182129</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>11.11325168609619</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>9.236356735229492</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>9.45839786529541</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>8.519502639770508</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>8.712535858154297</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>person 5</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Shourya_2.ogg</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>dataset\person 5\Shourya_2.ogg</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>-304.3930969238281</v>
+      </c>
+      <c r="E71" t="n">
+        <v>110.9409027099609</v>
+      </c>
+      <c r="F71" t="n">
+        <v>22.86139297485352</v>
+      </c>
+      <c r="G71" t="n">
+        <v>9.929296493530273</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-3.179068803787231</v>
+      </c>
+      <c r="I71" t="n">
+        <v>7.390394687652588</v>
+      </c>
+      <c r="J71" t="n">
+        <v>-7.251555919647217</v>
+      </c>
+      <c r="K71" t="n">
+        <v>5.896897792816162</v>
+      </c>
+      <c r="L71" t="n">
+        <v>-3.324414491653442</v>
+      </c>
+      <c r="M71" t="n">
+        <v>-7.386799335479736</v>
+      </c>
+      <c r="N71" t="n">
+        <v>-4.624073505401611</v>
+      </c>
+      <c r="O71" t="n">
+        <v>6.68902587890625</v>
+      </c>
+      <c r="P71" t="n">
+        <v>-4.714010715484619</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>91.78868865966797</v>
+      </c>
+      <c r="R71" t="n">
+        <v>62.5364990234375</v>
+      </c>
+      <c r="S71" t="n">
+        <v>29.78198432922363</v>
+      </c>
+      <c r="T71" t="n">
+        <v>32.40509796142578</v>
+      </c>
+      <c r="U71" t="n">
+        <v>20.26198577880859</v>
+      </c>
+      <c r="V71" t="n">
+        <v>14.40401840209961</v>
+      </c>
+      <c r="W71" t="n">
+        <v>18.52730178833008</v>
+      </c>
+      <c r="X71" t="n">
+        <v>12.89473533630371</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>11.26882934570312</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>11.64115619659424</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>10.10405349731445</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>8.079475402832031</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>8.508294105529785</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>person 6</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Tejender_1.ogg</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>dataset\person 6\Tejender_1.ogg</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>-241.2238159179688</v>
+      </c>
+      <c r="E72" t="n">
+        <v>130.6345672607422</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-12.36108493804932</v>
+      </c>
+      <c r="G72" t="n">
+        <v>13.04714488983154</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.2612474262714386</v>
+      </c>
+      <c r="I72" t="n">
+        <v>-14.38956260681152</v>
+      </c>
+      <c r="J72" t="n">
+        <v>-12.22889137268066</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-2.16316032409668</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-8.592954635620117</v>
+      </c>
+      <c r="M72" t="n">
+        <v>-12.96053504943848</v>
+      </c>
+      <c r="N72" t="n">
+        <v>3.854934453964233</v>
+      </c>
+      <c r="O72" t="n">
+        <v>-4.597562789916992</v>
+      </c>
+      <c r="P72" t="n">
+        <v>-8.279567718505859</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>97.86956024169922</v>
+      </c>
+      <c r="R72" t="n">
+        <v>57.71438980102539</v>
+      </c>
+      <c r="S72" t="n">
+        <v>46.75894927978516</v>
+      </c>
+      <c r="T72" t="n">
+        <v>32.36280822753906</v>
+      </c>
+      <c r="U72" t="n">
+        <v>18.50816535949707</v>
+      </c>
+      <c r="V72" t="n">
+        <v>22.63165855407715</v>
+      </c>
+      <c r="W72" t="n">
+        <v>18.74880218505859</v>
+      </c>
+      <c r="X72" t="n">
+        <v>11.94958877563477</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>14.44866466522217</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>12.14589977264404</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>10.23093128204346</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>9.25855827331543</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>10.18418788909912</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>person 6</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Tejender_2.ogg</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>dataset\person 6\Tejender_2.ogg</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>-279.4379577636719</v>
+      </c>
+      <c r="E73" t="n">
+        <v>133.3796234130859</v>
+      </c>
+      <c r="F73" t="n">
+        <v>-32.24570465087891</v>
+      </c>
+      <c r="G73" t="n">
+        <v>33.45166015625</v>
+      </c>
+      <c r="H73" t="n">
+        <v>20.97794532775879</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1.798129558563232</v>
+      </c>
+      <c r="J73" t="n">
+        <v>-17.07165145874023</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-9.722966194152832</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-7.129319190979004</v>
+      </c>
+      <c r="M73" t="n">
+        <v>-11.12513542175293</v>
+      </c>
+      <c r="N73" t="n">
+        <v>-0.7795337438583374</v>
+      </c>
+      <c r="O73" t="n">
+        <v>-5.830524444580078</v>
+      </c>
+      <c r="P73" t="n">
+        <v>-6.15012264251709</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>104.7699127197266</v>
+      </c>
+      <c r="R73" t="n">
+        <v>53.32034683227539</v>
+      </c>
+      <c r="S73" t="n">
+        <v>52.46269226074219</v>
+      </c>
+      <c r="T73" t="n">
+        <v>32.73448944091797</v>
+      </c>
+      <c r="U73" t="n">
+        <v>25.35870552062988</v>
+      </c>
+      <c r="V73" t="n">
+        <v>22.62563133239746</v>
+      </c>
+      <c r="W73" t="n">
+        <v>19.90865898132324</v>
+      </c>
+      <c r="X73" t="n">
+        <v>15.17664623260498</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>15.14743232727051</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>11.42538166046143</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>9.400094985961914</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>8.645046234130859</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>8.31033992767334</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>person 7</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>jheel_1.ogg</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>dataset\person 7\jheel_1.ogg</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>-317.1886596679688</v>
+      </c>
+      <c r="E74" t="n">
+        <v>139.5738220214844</v>
+      </c>
+      <c r="F74" t="n">
+        <v>24.0166072845459</v>
+      </c>
+      <c r="G74" t="n">
+        <v>14.53670024871826</v>
+      </c>
+      <c r="H74" t="n">
+        <v>8.242179870605469</v>
+      </c>
+      <c r="I74" t="n">
+        <v>3.172555685043335</v>
+      </c>
+      <c r="J74" t="n">
+        <v>-21.8743782043457</v>
+      </c>
+      <c r="K74" t="n">
+        <v>2.076800346374512</v>
+      </c>
+      <c r="L74" t="n">
+        <v>-8.145941734313965</v>
+      </c>
+      <c r="M74" t="n">
+        <v>-6.731777191162109</v>
+      </c>
+      <c r="N74" t="n">
+        <v>-7.22862434387207</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1.637333869934082</v>
+      </c>
+      <c r="P74" t="n">
+        <v>5.000531673431396</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>77.30405426025391</v>
+      </c>
+      <c r="R74" t="n">
+        <v>41.21332931518555</v>
+      </c>
+      <c r="S74" t="n">
+        <v>32.35728073120117</v>
+      </c>
+      <c r="T74" t="n">
+        <v>27.92392349243164</v>
+      </c>
+      <c r="U74" t="n">
+        <v>15.14712429046631</v>
+      </c>
+      <c r="V74" t="n">
+        <v>13.10469722747803</v>
+      </c>
+      <c r="W74" t="n">
+        <v>17.39910125732422</v>
+      </c>
+      <c r="X74" t="n">
+        <v>14.41896820068359</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>13.33712196350098</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>8.719347953796387</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>11.32425308227539</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>8.552587509155273</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>9.569530487060547</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>person 7</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>jheel_2.ogg</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>dataset\person 7\jheel_2.ogg</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>-229.3513336181641</v>
+      </c>
+      <c r="E75" t="n">
+        <v>99.31137084960938</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.41466331481934</v>
+      </c>
+      <c r="G75" t="n">
+        <v>13.3733549118042</v>
+      </c>
+      <c r="H75" t="n">
+        <v>3.016288757324219</v>
+      </c>
+      <c r="I75" t="n">
+        <v>-12.59360885620117</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-13.31148147583008</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-2.699369430541992</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-6.242746353149414</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-9.442974090576172</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1.134596467018127</v>
+      </c>
+      <c r="O75" t="n">
+        <v>-3.44888162612915</v>
+      </c>
+      <c r="P75" t="n">
+        <v>3.6424241065979</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>111.5307312011719</v>
+      </c>
+      <c r="R75" t="n">
+        <v>41.49425506591797</v>
+      </c>
+      <c r="S75" t="n">
+        <v>41.6881103515625</v>
+      </c>
+      <c r="T75" t="n">
+        <v>28.65260314941406</v>
+      </c>
+      <c r="U75" t="n">
+        <v>16.42165946960449</v>
+      </c>
+      <c r="V75" t="n">
+        <v>18.10476875305176</v>
+      </c>
+      <c r="W75" t="n">
+        <v>14.88711261749268</v>
+      </c>
+      <c r="X75" t="n">
+        <v>14.33713817596436</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>13.68465805053711</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>10.41324424743652</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>11.4205846786499</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>12.3576831817627</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>9.243979454040527</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>person 8</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ankita_1.ogg</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>dataset\person 8\ankita_1.ogg</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>-270.2237243652344</v>
+      </c>
+      <c r="E76" t="n">
+        <v>58.96270751953125</v>
+      </c>
+      <c r="F76" t="n">
+        <v>38.67244720458984</v>
+      </c>
+      <c r="G76" t="n">
+        <v>8.070169448852539</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-24.42742538452148</v>
+      </c>
+      <c r="I76" t="n">
+        <v>2.1974196434021</v>
+      </c>
+      <c r="J76" t="n">
+        <v>-7.311805248260498</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-10.53012466430664</v>
+      </c>
+      <c r="L76" t="n">
+        <v>-5.142326354980469</v>
+      </c>
+      <c r="M76" t="n">
+        <v>-2.67604398727417</v>
+      </c>
+      <c r="N76" t="n">
+        <v>-12.98607063293457</v>
+      </c>
+      <c r="O76" t="n">
+        <v>-10.37759876251221</v>
+      </c>
+      <c r="P76" t="n">
+        <v>-8.26213550567627</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>122.35009765625</v>
+      </c>
+      <c r="R76" t="n">
+        <v>53.08518600463867</v>
+      </c>
+      <c r="S76" t="n">
+        <v>39.09588241577148</v>
+      </c>
+      <c r="T76" t="n">
+        <v>27.46438217163086</v>
+      </c>
+      <c r="U76" t="n">
+        <v>28.98434257507324</v>
+      </c>
+      <c r="V76" t="n">
+        <v>15.67507457733154</v>
+      </c>
+      <c r="W76" t="n">
+        <v>14.56611728668213</v>
+      </c>
+      <c r="X76" t="n">
+        <v>14.58829212188721</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>12.29934310913086</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>10.6221866607666</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>10.70013236999512</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>10.061936378479</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>9.220752716064453</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>person 8</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ankita_2.ogg</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>dataset\person 8\ankita_2.ogg</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>-250.0560913085938</v>
+      </c>
+      <c r="E77" t="n">
+        <v>72.12837219238281</v>
+      </c>
+      <c r="F77" t="n">
+        <v>34.50404357910156</v>
+      </c>
+      <c r="G77" t="n">
+        <v>5.64661693572998</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-31.13961982727051</v>
+      </c>
+      <c r="I77" t="n">
+        <v>-1.317376494407654</v>
+      </c>
+      <c r="J77" t="n">
+        <v>-10.20572566986084</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-14.19919300079346</v>
+      </c>
+      <c r="L77" t="n">
+        <v>-4.693023681640625</v>
+      </c>
+      <c r="M77" t="n">
+        <v>-2.679990768432617</v>
+      </c>
+      <c r="N77" t="n">
+        <v>-15.13342761993408</v>
+      </c>
+      <c r="O77" t="n">
+        <v>-7.792290687561035</v>
+      </c>
+      <c r="P77" t="n">
+        <v>-9.90543270111084</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>119.1896743774414</v>
+      </c>
+      <c r="R77" t="n">
+        <v>51.60607147216797</v>
+      </c>
+      <c r="S77" t="n">
+        <v>37.96743011474609</v>
+      </c>
+      <c r="T77" t="n">
+        <v>28.75864028930664</v>
+      </c>
+      <c r="U77" t="n">
+        <v>29.4977855682373</v>
+      </c>
+      <c r="V77" t="n">
+        <v>17.02374649047852</v>
+      </c>
+      <c r="W77" t="n">
+        <v>14.97891616821289</v>
+      </c>
+      <c r="X77" t="n">
+        <v>14.13392162322998</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>12.5789794921875</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>10.51625442504883</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>10.5496711730957</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>9.269749641418457</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>9.096851348876953</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>person 8</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ankita_4.ogg</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>dataset\person 8\ankita_4.ogg</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>-258.3805236816406</v>
+      </c>
+      <c r="E78" t="n">
+        <v>92.83200073242188</v>
+      </c>
+      <c r="F78" t="n">
+        <v>11.39120864868164</v>
+      </c>
+      <c r="G78" t="n">
+        <v>6.207101821899414</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2.089468240737915</v>
+      </c>
+      <c r="I78" t="n">
+        <v>-20.39954376220703</v>
+      </c>
+      <c r="J78" t="n">
+        <v>-11.28644371032715</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-8.85013484954834</v>
+      </c>
+      <c r="L78" t="n">
+        <v>-0.6754090785980225</v>
+      </c>
+      <c r="M78" t="n">
+        <v>-11.15882301330566</v>
+      </c>
+      <c r="N78" t="n">
+        <v>-12.50483322143555</v>
+      </c>
+      <c r="O78" t="n">
+        <v>-8.705537796020508</v>
+      </c>
+      <c r="P78" t="n">
+        <v>-8.155506134033203</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>106.4656829833984</v>
+      </c>
+      <c r="R78" t="n">
+        <v>48.88466262817383</v>
+      </c>
+      <c r="S78" t="n">
+        <v>35.45600891113281</v>
+      </c>
+      <c r="T78" t="n">
+        <v>32.61907577514648</v>
+      </c>
+      <c r="U78" t="n">
+        <v>22.51460838317871</v>
+      </c>
+      <c r="V78" t="n">
+        <v>20.42388534545898</v>
+      </c>
+      <c r="W78" t="n">
+        <v>14.98693084716797</v>
+      </c>
+      <c r="X78" t="n">
+        <v>14.11903953552246</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>14.4618616104126</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>9.938737869262695</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>9.666037559509277</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>10.90330410003662</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>9.622568130493164</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>person 9</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>vaishnavi_1.ogg</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>dataset\person 9\vaishnavi_1.ogg</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>-256.3796081542969</v>
+      </c>
+      <c r="E79" t="n">
+        <v>98.49275970458984</v>
+      </c>
+      <c r="F79" t="n">
+        <v>8.732111930847168</v>
+      </c>
+      <c r="G79" t="n">
+        <v>30.44884872436523</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-7.923402309417725</v>
+      </c>
+      <c r="I79" t="n">
+        <v>-7.455092430114746</v>
+      </c>
+      <c r="J79" t="n">
+        <v>-19.39515495300293</v>
+      </c>
+      <c r="K79" t="n">
+        <v>-19.24704360961914</v>
+      </c>
+      <c r="L79" t="n">
+        <v>-4.155113697052002</v>
+      </c>
+      <c r="M79" t="n">
+        <v>-9.748040199279785</v>
+      </c>
+      <c r="N79" t="n">
+        <v>-8.807007789611816</v>
+      </c>
+      <c r="O79" t="n">
+        <v>-6.999690055847168</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.4338657259941101</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>121.5381088256836</v>
+      </c>
+      <c r="R79" t="n">
+        <v>39.5520133972168</v>
+      </c>
+      <c r="S79" t="n">
+        <v>45.04905700683594</v>
+      </c>
+      <c r="T79" t="n">
+        <v>25.2275562286377</v>
+      </c>
+      <c r="U79" t="n">
+        <v>26.77007865905762</v>
+      </c>
+      <c r="V79" t="n">
+        <v>13.50710296630859</v>
+      </c>
+      <c r="W79" t="n">
+        <v>14.61097717285156</v>
+      </c>
+      <c r="X79" t="n">
+        <v>15.18807888031006</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>13.30795669555664</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>11.20494937896729</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>10.87530899047852</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>11.49388599395752</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>8.31267261505127</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>person 9</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
         <is>
           <t>vaishnavi_3.ogg</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>dataset\person 9\vaishnavi_3.ogg</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D80" t="n">
         <v>-251.5499725341797</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E80" t="n">
         <v>92.1644287109375</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F80" t="n">
         <v>6.074502944946289</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G80" t="n">
         <v>33.25386810302734</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H80" t="n">
         <v>-8.293931007385254</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I80" t="n">
         <v>-15.41576957702637</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J80" t="n">
         <v>-23.28523445129395</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K80" t="n">
         <v>-15.47053337097168</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L80" t="n">
         <v>-5.091086387634277</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M80" t="n">
         <v>-11.46393871307373</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N80" t="n">
         <v>-7.56251335144043</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O80" t="n">
         <v>-7.744572162628174</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P80" t="n">
         <v>0.3262795209884644</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q80" t="n">
         <v>114.1080551147461</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R80" t="n">
         <v>40.90968322753906</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S80" t="n">
         <v>44.52767944335938</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T80" t="n">
         <v>30.35942077636719</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U80" t="n">
         <v>25.61916351318359</v>
       </c>
-      <c r="V22" t="n">
+      <c r="V80" t="n">
         <v>15.83772468566895</v>
       </c>
-      <c r="W22" t="n">
+      <c r="W80" t="n">
         <v>15.28616619110107</v>
       </c>
-      <c r="X22" t="n">
+      <c r="X80" t="n">
         <v>13.24298763275146</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="Y80" t="n">
         <v>13.70436096191406</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="Z80" t="n">
         <v>11.20803642272949</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AA80" t="n">
         <v>9.892670631408691</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AB80" t="n">
         <v>11.61030101776123</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AC80" t="n">
         <v>8.742694854736328</v>
       </c>
     </row>

--- a/outputs/mfcc_features.xlsx
+++ b/outputs/mfcc_features.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC80"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7038,1045 +7038,1615 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>person 5</t>
+          <t>person 40</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Shourya_1.ogg</t>
+          <t>divyanshi_1.ogg</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>dataset\person 5\Shourya_1.ogg</t>
+          <t>dataset\person 40\divyanshi_1.ogg</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-358.8090515136719</v>
+        <v>-244.3163299560547</v>
       </c>
       <c r="E70" t="n">
-        <v>114.3142395019531</v>
+        <v>105.2449111938477</v>
       </c>
       <c r="F70" t="n">
-        <v>37.55840682983398</v>
+        <v>6.909623622894287</v>
       </c>
       <c r="G70" t="n">
-        <v>13.92228031158447</v>
+        <v>24.58787536621094</v>
       </c>
       <c r="H70" t="n">
-        <v>1.206528663635254</v>
+        <v>3.22581148147583</v>
       </c>
       <c r="I70" t="n">
-        <v>6.434402942657471</v>
+        <v>-1.036438226699829</v>
       </c>
       <c r="J70" t="n">
-        <v>-8.759699821472168</v>
+        <v>-34.69623947143555</v>
       </c>
       <c r="K70" t="n">
-        <v>0.6461262702941895</v>
+        <v>-14.00222492218018</v>
       </c>
       <c r="L70" t="n">
-        <v>-2.814217090606689</v>
+        <v>-4.365294456481934</v>
       </c>
       <c r="M70" t="n">
-        <v>-3.152784109115601</v>
+        <v>-18.07063484191895</v>
       </c>
       <c r="N70" t="n">
-        <v>1.124211668968201</v>
+        <v>-0.3718851506710052</v>
       </c>
       <c r="O70" t="n">
-        <v>2.428881645202637</v>
+        <v>-12.72995185852051</v>
       </c>
       <c r="P70" t="n">
-        <v>-3.400106191635132</v>
+        <v>-7.532426357269287</v>
       </c>
       <c r="Q70" t="n">
-        <v>89.46620941162109</v>
+        <v>75.8829345703125</v>
       </c>
       <c r="R70" t="n">
-        <v>61.67924499511719</v>
+        <v>46.22599029541016</v>
       </c>
       <c r="S70" t="n">
-        <v>28.91465950012207</v>
+        <v>37.79397964477539</v>
       </c>
       <c r="T70" t="n">
-        <v>31.10330772399902</v>
+        <v>29.9464282989502</v>
       </c>
       <c r="U70" t="n">
-        <v>17.80472946166992</v>
+        <v>19.67901611328125</v>
       </c>
       <c r="V70" t="n">
-        <v>16.71832847595215</v>
+        <v>16.33155059814453</v>
       </c>
       <c r="W70" t="n">
-        <v>18.56906890869141</v>
+        <v>20.31580352783203</v>
       </c>
       <c r="X70" t="n">
-        <v>13.13578224182129</v>
+        <v>13.87296390533447</v>
       </c>
       <c r="Y70" t="n">
-        <v>11.11325168609619</v>
+        <v>15.97002983093262</v>
       </c>
       <c r="Z70" t="n">
-        <v>9.236356735229492</v>
+        <v>11.06313133239746</v>
       </c>
       <c r="AA70" t="n">
-        <v>9.45839786529541</v>
+        <v>12.70590877532959</v>
       </c>
       <c r="AB70" t="n">
-        <v>8.519502639770508</v>
+        <v>11.95295715332031</v>
       </c>
       <c r="AC70" t="n">
-        <v>8.712535858154297</v>
+        <v>10.15397262573242</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>person 5</t>
+          <t>person 40</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Shourya_2.ogg</t>
+          <t>divyanshi_2.ogg</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>dataset\person 5\Shourya_2.ogg</t>
+          <t>dataset\person 40\divyanshi_2.ogg</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-304.3930969238281</v>
+        <v>-227.1504974365234</v>
       </c>
       <c r="E71" t="n">
-        <v>110.9409027099609</v>
+        <v>108.2984008789062</v>
       </c>
       <c r="F71" t="n">
-        <v>22.86139297485352</v>
+        <v>3.270785331726074</v>
       </c>
       <c r="G71" t="n">
-        <v>9.929296493530273</v>
+        <v>30.84189796447754</v>
       </c>
       <c r="H71" t="n">
-        <v>-3.179068803787231</v>
+        <v>-1.194762945175171</v>
       </c>
       <c r="I71" t="n">
-        <v>7.390394687652588</v>
+        <v>2.510217666625977</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.251555919647217</v>
+        <v>-37.22833251953125</v>
       </c>
       <c r="K71" t="n">
-        <v>5.896897792816162</v>
+        <v>-23.99452590942383</v>
       </c>
       <c r="L71" t="n">
-        <v>-3.324414491653442</v>
+        <v>-3.880319833755493</v>
       </c>
       <c r="M71" t="n">
-        <v>-7.386799335479736</v>
+        <v>-16.44269180297852</v>
       </c>
       <c r="N71" t="n">
-        <v>-4.624073505401611</v>
+        <v>-3.170436382293701</v>
       </c>
       <c r="O71" t="n">
-        <v>6.68902587890625</v>
+        <v>-9.912579536437988</v>
       </c>
       <c r="P71" t="n">
-        <v>-4.714010715484619</v>
+        <v>-5.463229179382324</v>
       </c>
       <c r="Q71" t="n">
-        <v>91.78868865966797</v>
+        <v>79.82475280761719</v>
       </c>
       <c r="R71" t="n">
-        <v>62.5364990234375</v>
+        <v>43.07849884033203</v>
       </c>
       <c r="S71" t="n">
-        <v>29.78198432922363</v>
+        <v>37.13301467895508</v>
       </c>
       <c r="T71" t="n">
-        <v>32.40509796142578</v>
+        <v>27.5322322845459</v>
       </c>
       <c r="U71" t="n">
-        <v>20.26198577880859</v>
+        <v>19.55008888244629</v>
       </c>
       <c r="V71" t="n">
-        <v>14.40401840209961</v>
+        <v>15.23422336578369</v>
       </c>
       <c r="W71" t="n">
-        <v>18.52730178833008</v>
+        <v>21.08696556091309</v>
       </c>
       <c r="X71" t="n">
-        <v>12.89473533630371</v>
+        <v>14.93356132507324</v>
       </c>
       <c r="Y71" t="n">
-        <v>11.26882934570312</v>
+        <v>16.830810546875</v>
       </c>
       <c r="Z71" t="n">
-        <v>11.64115619659424</v>
+        <v>11.18288230895996</v>
       </c>
       <c r="AA71" t="n">
-        <v>10.10405349731445</v>
+        <v>12.12485694885254</v>
       </c>
       <c r="AB71" t="n">
-        <v>8.079475402832031</v>
+        <v>10.52318382263184</v>
       </c>
       <c r="AC71" t="n">
-        <v>8.508294105529785</v>
+        <v>10.00053405761719</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>person 6</t>
+          <t>person 41</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tejender_1.ogg</t>
+          <t>anshil_1.ogg</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>dataset\person 6\Tejender_1.ogg</t>
+          <t>dataset\person 41\anshil_1.ogg</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>-241.2238159179688</v>
+        <v>-331.8249206542969</v>
       </c>
       <c r="E72" t="n">
-        <v>130.6345672607422</v>
+        <v>62.13373184204102</v>
       </c>
       <c r="F72" t="n">
-        <v>-12.36108493804932</v>
+        <v>43.34157562255859</v>
       </c>
       <c r="G72" t="n">
-        <v>13.04714488983154</v>
+        <v>30.13431930541992</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2612474262714386</v>
+        <v>5.614983081817627</v>
       </c>
       <c r="I72" t="n">
-        <v>-14.38956260681152</v>
+        <v>-2.005221128463745</v>
       </c>
       <c r="J72" t="n">
-        <v>-12.22889137268066</v>
+        <v>-9.269699096679688</v>
       </c>
       <c r="K72" t="n">
-        <v>-2.16316032409668</v>
+        <v>-7.635746955871582</v>
       </c>
       <c r="L72" t="n">
-        <v>-8.592954635620117</v>
+        <v>-12.83535194396973</v>
       </c>
       <c r="M72" t="n">
-        <v>-12.96053504943848</v>
+        <v>-12.20539569854736</v>
       </c>
       <c r="N72" t="n">
-        <v>3.854934453964233</v>
+        <v>-15.36096668243408</v>
       </c>
       <c r="O72" t="n">
-        <v>-4.597562789916992</v>
+        <v>-15.3010311126709</v>
       </c>
       <c r="P72" t="n">
-        <v>-8.279567718505859</v>
+        <v>-19.25372695922852</v>
       </c>
       <c r="Q72" t="n">
-        <v>97.86956024169922</v>
+        <v>124.8133010864258</v>
       </c>
       <c r="R72" t="n">
-        <v>57.71438980102539</v>
+        <v>55.68733596801758</v>
       </c>
       <c r="S72" t="n">
-        <v>46.75894927978516</v>
+        <v>36.07352066040039</v>
       </c>
       <c r="T72" t="n">
-        <v>32.36280822753906</v>
+        <v>35.21308135986328</v>
       </c>
       <c r="U72" t="n">
-        <v>18.50816535949707</v>
+        <v>19.98479270935059</v>
       </c>
       <c r="V72" t="n">
-        <v>22.63165855407715</v>
+        <v>18.27727890014648</v>
       </c>
       <c r="W72" t="n">
-        <v>18.74880218505859</v>
+        <v>15.03438282012939</v>
       </c>
       <c r="X72" t="n">
-        <v>11.94958877563477</v>
+        <v>13.22131252288818</v>
       </c>
       <c r="Y72" t="n">
-        <v>14.44866466522217</v>
+        <v>13.85098934173584</v>
       </c>
       <c r="Z72" t="n">
-        <v>12.14589977264404</v>
+        <v>15.40560913085938</v>
       </c>
       <c r="AA72" t="n">
-        <v>10.23093128204346</v>
+        <v>11.00161457061768</v>
       </c>
       <c r="AB72" t="n">
-        <v>9.25855827331543</v>
+        <v>10.687255859375</v>
       </c>
       <c r="AC72" t="n">
-        <v>10.18418788909912</v>
+        <v>11.76873683929443</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>person 6</t>
+          <t>person 41</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tejender_2.ogg</t>
+          <t>anshil_2.ogg</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>dataset\person 6\Tejender_2.ogg</t>
+          <t>dataset\person 41\anshil_2.ogg</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>-279.4379577636719</v>
+        <v>-313.7524108886719</v>
       </c>
       <c r="E73" t="n">
-        <v>133.3796234130859</v>
+        <v>87.83678436279297</v>
       </c>
       <c r="F73" t="n">
-        <v>-32.24570465087891</v>
+        <v>32.08012390136719</v>
       </c>
       <c r="G73" t="n">
-        <v>33.45166015625</v>
+        <v>27.53726577758789</v>
       </c>
       <c r="H73" t="n">
-        <v>20.97794532775879</v>
+        <v>10.16057968139648</v>
       </c>
       <c r="I73" t="n">
-        <v>1.798129558563232</v>
+        <v>-11.46732425689697</v>
       </c>
       <c r="J73" t="n">
-        <v>-17.07165145874023</v>
+        <v>-8.61205005645752</v>
       </c>
       <c r="K73" t="n">
-        <v>-9.722966194152832</v>
+        <v>-11.30067157745361</v>
       </c>
       <c r="L73" t="n">
-        <v>-7.129319190979004</v>
+        <v>-11.63246250152588</v>
       </c>
       <c r="M73" t="n">
-        <v>-11.12513542175293</v>
+        <v>-7.211940288543701</v>
       </c>
       <c r="N73" t="n">
-        <v>-0.7795337438583374</v>
+        <v>-20.88786125183105</v>
       </c>
       <c r="O73" t="n">
-        <v>-5.830524444580078</v>
+        <v>-14.47123241424561</v>
       </c>
       <c r="P73" t="n">
-        <v>-6.15012264251709</v>
+        <v>-20.77337265014648</v>
       </c>
       <c r="Q73" t="n">
-        <v>104.7699127197266</v>
+        <v>115.6270294189453</v>
       </c>
       <c r="R73" t="n">
-        <v>53.32034683227539</v>
+        <v>56.92110061645508</v>
       </c>
       <c r="S73" t="n">
-        <v>52.46269226074219</v>
+        <v>31.04143333435059</v>
       </c>
       <c r="T73" t="n">
-        <v>32.73448944091797</v>
+        <v>33.25688934326172</v>
       </c>
       <c r="U73" t="n">
-        <v>25.35870552062988</v>
+        <v>19.39156723022461</v>
       </c>
       <c r="V73" t="n">
-        <v>22.62563133239746</v>
+        <v>18.62007904052734</v>
       </c>
       <c r="W73" t="n">
-        <v>19.90865898132324</v>
+        <v>15.31217193603516</v>
       </c>
       <c r="X73" t="n">
-        <v>15.17664623260498</v>
+        <v>13.42257499694824</v>
       </c>
       <c r="Y73" t="n">
-        <v>15.14743232727051</v>
+        <v>12.59476375579834</v>
       </c>
       <c r="Z73" t="n">
-        <v>11.42538166046143</v>
+        <v>13.32803058624268</v>
       </c>
       <c r="AA73" t="n">
-        <v>9.400094985961914</v>
+        <v>11.81994438171387</v>
       </c>
       <c r="AB73" t="n">
-        <v>8.645046234130859</v>
+        <v>11.3255033493042</v>
       </c>
       <c r="AC73" t="n">
-        <v>8.31033992767334</v>
+        <v>12.41770553588867</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>person 7</t>
+          <t>person 42</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jheel_1.ogg</t>
+          <t>pradeep_1.ogg</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>dataset\person 7\jheel_1.ogg</t>
+          <t>dataset\person 42\pradeep_1.ogg</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>-317.1886596679688</v>
+        <v>-232.788818359375</v>
       </c>
       <c r="E74" t="n">
-        <v>139.5738220214844</v>
+        <v>115.4244613647461</v>
       </c>
       <c r="F74" t="n">
-        <v>24.0166072845459</v>
+        <v>8.951861381530762</v>
       </c>
       <c r="G74" t="n">
-        <v>14.53670024871826</v>
+        <v>35.44657516479492</v>
       </c>
       <c r="H74" t="n">
-        <v>8.242179870605469</v>
+        <v>-10.6364860534668</v>
       </c>
       <c r="I74" t="n">
-        <v>3.172555685043335</v>
+        <v>-14.63413906097412</v>
       </c>
       <c r="J74" t="n">
-        <v>-21.8743782043457</v>
+        <v>-21.84220695495605</v>
       </c>
       <c r="K74" t="n">
-        <v>2.076800346374512</v>
+        <v>-12.38983058929443</v>
       </c>
       <c r="L74" t="n">
-        <v>-8.145941734313965</v>
+        <v>-10.26648330688477</v>
       </c>
       <c r="M74" t="n">
-        <v>-6.731777191162109</v>
+        <v>-20.43499946594238</v>
       </c>
       <c r="N74" t="n">
-        <v>-7.22862434387207</v>
+        <v>-3.28559398651123</v>
       </c>
       <c r="O74" t="n">
-        <v>1.637333869934082</v>
+        <v>-7.053805828094482</v>
       </c>
       <c r="P74" t="n">
-        <v>5.000531673431396</v>
+        <v>-4.129644393920898</v>
       </c>
       <c r="Q74" t="n">
-        <v>77.30405426025391</v>
+        <v>72.32980346679688</v>
       </c>
       <c r="R74" t="n">
-        <v>41.21332931518555</v>
+        <v>51.19033432006836</v>
       </c>
       <c r="S74" t="n">
-        <v>32.35728073120117</v>
+        <v>30.75857162475586</v>
       </c>
       <c r="T74" t="n">
-        <v>27.92392349243164</v>
+        <v>30.71547508239746</v>
       </c>
       <c r="U74" t="n">
-        <v>15.14712429046631</v>
+        <v>17.53998947143555</v>
       </c>
       <c r="V74" t="n">
-        <v>13.10469722747803</v>
+        <v>15.4393949508667</v>
       </c>
       <c r="W74" t="n">
-        <v>17.39910125732422</v>
+        <v>15.77964019775391</v>
       </c>
       <c r="X74" t="n">
-        <v>14.41896820068359</v>
+        <v>13.03182601928711</v>
       </c>
       <c r="Y74" t="n">
-        <v>13.33712196350098</v>
+        <v>12.89509201049805</v>
       </c>
       <c r="Z74" t="n">
-        <v>8.719347953796387</v>
+        <v>14.75205612182617</v>
       </c>
       <c r="AA74" t="n">
-        <v>11.32425308227539</v>
+        <v>9.207385063171387</v>
       </c>
       <c r="AB74" t="n">
-        <v>8.552587509155273</v>
+        <v>9.575556755065918</v>
       </c>
       <c r="AC74" t="n">
-        <v>9.569530487060547</v>
+        <v>8.402165412902832</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>person 7</t>
+          <t>person 42</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jheel_2.ogg</t>
+          <t>pradeep_2.ogg</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>dataset\person 7\jheel_2.ogg</t>
+          <t>dataset\person 42\pradeep_2.ogg</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>-229.3513336181641</v>
+        <v>-219.2324829101562</v>
       </c>
       <c r="E75" t="n">
-        <v>99.31137084960938</v>
+        <v>102.2283020019531</v>
       </c>
       <c r="F75" t="n">
-        <v>13.41466331481934</v>
+        <v>5.340405464172363</v>
       </c>
       <c r="G75" t="n">
-        <v>13.3733549118042</v>
+        <v>36.30477905273438</v>
       </c>
       <c r="H75" t="n">
-        <v>3.016288757324219</v>
+        <v>-4.958206653594971</v>
       </c>
       <c r="I75" t="n">
-        <v>-12.59360885620117</v>
+        <v>-15.88275718688965</v>
       </c>
       <c r="J75" t="n">
-        <v>-13.31148147583008</v>
+        <v>-32.45648956298828</v>
       </c>
       <c r="K75" t="n">
-        <v>-2.699369430541992</v>
+        <v>-6.66447114944458</v>
       </c>
       <c r="L75" t="n">
-        <v>-6.242746353149414</v>
+        <v>-15.98520469665527</v>
       </c>
       <c r="M75" t="n">
-        <v>-9.442974090576172</v>
+        <v>-22.49023818969727</v>
       </c>
       <c r="N75" t="n">
-        <v>1.134596467018127</v>
+        <v>-2.657112121582031</v>
       </c>
       <c r="O75" t="n">
-        <v>-3.44888162612915</v>
+        <v>-6.286296367645264</v>
       </c>
       <c r="P75" t="n">
-        <v>3.6424241065979</v>
+        <v>-2.275124073028564</v>
       </c>
       <c r="Q75" t="n">
-        <v>111.5307312011719</v>
+        <v>73.91389465332031</v>
       </c>
       <c r="R75" t="n">
-        <v>41.49425506591797</v>
+        <v>58.17205047607422</v>
       </c>
       <c r="S75" t="n">
-        <v>41.6881103515625</v>
+        <v>28.82460975646973</v>
       </c>
       <c r="T75" t="n">
-        <v>28.65260314941406</v>
+        <v>36.22875213623047</v>
       </c>
       <c r="U75" t="n">
-        <v>16.42165946960449</v>
+        <v>18.28576278686523</v>
       </c>
       <c r="V75" t="n">
-        <v>18.10476875305176</v>
+        <v>16.65082550048828</v>
       </c>
       <c r="W75" t="n">
-        <v>14.88711261749268</v>
+        <v>17.05229759216309</v>
       </c>
       <c r="X75" t="n">
-        <v>14.33713817596436</v>
+        <v>11.97657012939453</v>
       </c>
       <c r="Y75" t="n">
-        <v>13.68465805053711</v>
+        <v>12.1724681854248</v>
       </c>
       <c r="Z75" t="n">
-        <v>10.41324424743652</v>
+        <v>13.96055889129639</v>
       </c>
       <c r="AA75" t="n">
-        <v>11.4205846786499</v>
+        <v>9.730836868286133</v>
       </c>
       <c r="AB75" t="n">
-        <v>12.3576831817627</v>
+        <v>8.538913726806641</v>
       </c>
       <c r="AC75" t="n">
-        <v>9.243979454040527</v>
+        <v>8.958616256713867</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>person 8</t>
+          <t>person 5</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ankita_1.ogg</t>
+          <t>Shourya_1.ogg</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>dataset\person 8\ankita_1.ogg</t>
+          <t>dataset\person 5\Shourya_1.ogg</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>-270.2237243652344</v>
+        <v>-358.8090515136719</v>
       </c>
       <c r="E76" t="n">
-        <v>58.96270751953125</v>
+        <v>114.3142395019531</v>
       </c>
       <c r="F76" t="n">
-        <v>38.67244720458984</v>
+        <v>37.55840682983398</v>
       </c>
       <c r="G76" t="n">
-        <v>8.070169448852539</v>
+        <v>13.92228031158447</v>
       </c>
       <c r="H76" t="n">
-        <v>-24.42742538452148</v>
+        <v>1.206528663635254</v>
       </c>
       <c r="I76" t="n">
-        <v>2.1974196434021</v>
+        <v>6.434402942657471</v>
       </c>
       <c r="J76" t="n">
-        <v>-7.311805248260498</v>
+        <v>-8.759699821472168</v>
       </c>
       <c r="K76" t="n">
-        <v>-10.53012466430664</v>
+        <v>0.6461262702941895</v>
       </c>
       <c r="L76" t="n">
-        <v>-5.142326354980469</v>
+        <v>-2.814217090606689</v>
       </c>
       <c r="M76" t="n">
-        <v>-2.67604398727417</v>
+        <v>-3.152784109115601</v>
       </c>
       <c r="N76" t="n">
-        <v>-12.98607063293457</v>
+        <v>1.124211668968201</v>
       </c>
       <c r="O76" t="n">
-        <v>-10.37759876251221</v>
+        <v>2.428881645202637</v>
       </c>
       <c r="P76" t="n">
-        <v>-8.26213550567627</v>
+        <v>-3.400106191635132</v>
       </c>
       <c r="Q76" t="n">
-        <v>122.35009765625</v>
+        <v>89.46620941162109</v>
       </c>
       <c r="R76" t="n">
-        <v>53.08518600463867</v>
+        <v>61.67924499511719</v>
       </c>
       <c r="S76" t="n">
-        <v>39.09588241577148</v>
+        <v>28.91465950012207</v>
       </c>
       <c r="T76" t="n">
-        <v>27.46438217163086</v>
+        <v>31.10330772399902</v>
       </c>
       <c r="U76" t="n">
-        <v>28.98434257507324</v>
+        <v>17.80472946166992</v>
       </c>
       <c r="V76" t="n">
-        <v>15.67507457733154</v>
+        <v>16.71832847595215</v>
       </c>
       <c r="W76" t="n">
-        <v>14.56611728668213</v>
+        <v>18.56906890869141</v>
       </c>
       <c r="X76" t="n">
-        <v>14.58829212188721</v>
+        <v>13.13578224182129</v>
       </c>
       <c r="Y76" t="n">
-        <v>12.29934310913086</v>
+        <v>11.11325168609619</v>
       </c>
       <c r="Z76" t="n">
-        <v>10.6221866607666</v>
+        <v>9.236356735229492</v>
       </c>
       <c r="AA76" t="n">
-        <v>10.70013236999512</v>
+        <v>9.45839786529541</v>
       </c>
       <c r="AB76" t="n">
-        <v>10.061936378479</v>
+        <v>8.519502639770508</v>
       </c>
       <c r="AC76" t="n">
-        <v>9.220752716064453</v>
+        <v>8.712535858154297</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>person 8</t>
+          <t>person 5</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ankita_2.ogg</t>
+          <t>Shourya_2.ogg</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>dataset\person 8\ankita_2.ogg</t>
+          <t>dataset\person 5\Shourya_2.ogg</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>-250.0560913085938</v>
+        <v>-304.3930969238281</v>
       </c>
       <c r="E77" t="n">
-        <v>72.12837219238281</v>
+        <v>110.9409027099609</v>
       </c>
       <c r="F77" t="n">
-        <v>34.50404357910156</v>
+        <v>22.86139297485352</v>
       </c>
       <c r="G77" t="n">
-        <v>5.64661693572998</v>
+        <v>9.929296493530273</v>
       </c>
       <c r="H77" t="n">
-        <v>-31.13961982727051</v>
+        <v>-3.179068803787231</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.317376494407654</v>
+        <v>7.390394687652588</v>
       </c>
       <c r="J77" t="n">
-        <v>-10.20572566986084</v>
+        <v>-7.251555919647217</v>
       </c>
       <c r="K77" t="n">
-        <v>-14.19919300079346</v>
+        <v>5.896897792816162</v>
       </c>
       <c r="L77" t="n">
-        <v>-4.693023681640625</v>
+        <v>-3.324414491653442</v>
       </c>
       <c r="M77" t="n">
-        <v>-2.679990768432617</v>
+        <v>-7.386799335479736</v>
       </c>
       <c r="N77" t="n">
-        <v>-15.13342761993408</v>
+        <v>-4.624073505401611</v>
       </c>
       <c r="O77" t="n">
-        <v>-7.792290687561035</v>
+        <v>6.68902587890625</v>
       </c>
       <c r="P77" t="n">
-        <v>-9.90543270111084</v>
+        <v>-4.714010715484619</v>
       </c>
       <c r="Q77" t="n">
-        <v>119.1896743774414</v>
+        <v>91.78868865966797</v>
       </c>
       <c r="R77" t="n">
-        <v>51.60607147216797</v>
+        <v>62.5364990234375</v>
       </c>
       <c r="S77" t="n">
-        <v>37.96743011474609</v>
+        <v>29.78198432922363</v>
       </c>
       <c r="T77" t="n">
-        <v>28.75864028930664</v>
+        <v>32.40509796142578</v>
       </c>
       <c r="U77" t="n">
-        <v>29.4977855682373</v>
+        <v>20.26198577880859</v>
       </c>
       <c r="V77" t="n">
-        <v>17.02374649047852</v>
+        <v>14.40401840209961</v>
       </c>
       <c r="W77" t="n">
-        <v>14.97891616821289</v>
+        <v>18.52730178833008</v>
       </c>
       <c r="X77" t="n">
-        <v>14.13392162322998</v>
+        <v>12.89473533630371</v>
       </c>
       <c r="Y77" t="n">
-        <v>12.5789794921875</v>
+        <v>11.26882934570312</v>
       </c>
       <c r="Z77" t="n">
-        <v>10.51625442504883</v>
+        <v>11.64115619659424</v>
       </c>
       <c r="AA77" t="n">
-        <v>10.5496711730957</v>
+        <v>10.10405349731445</v>
       </c>
       <c r="AB77" t="n">
-        <v>9.269749641418457</v>
+        <v>8.079475402832031</v>
       </c>
       <c r="AC77" t="n">
-        <v>9.096851348876953</v>
+        <v>8.508294105529785</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>person 8</t>
+          <t>person 6</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ankita_4.ogg</t>
+          <t>Tejender_1.ogg</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>dataset\person 8\ankita_4.ogg</t>
+          <t>dataset\person 6\Tejender_1.ogg</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>-258.3805236816406</v>
+        <v>-241.2238159179688</v>
       </c>
       <c r="E78" t="n">
-        <v>92.83200073242188</v>
+        <v>130.6345672607422</v>
       </c>
       <c r="F78" t="n">
-        <v>11.39120864868164</v>
+        <v>-12.36108493804932</v>
       </c>
       <c r="G78" t="n">
-        <v>6.207101821899414</v>
+        <v>13.04714488983154</v>
       </c>
       <c r="H78" t="n">
-        <v>2.089468240737915</v>
+        <v>0.2612474262714386</v>
       </c>
       <c r="I78" t="n">
-        <v>-20.39954376220703</v>
+        <v>-14.38956260681152</v>
       </c>
       <c r="J78" t="n">
-        <v>-11.28644371032715</v>
+        <v>-12.22889137268066</v>
       </c>
       <c r="K78" t="n">
-        <v>-8.85013484954834</v>
+        <v>-2.16316032409668</v>
       </c>
       <c r="L78" t="n">
-        <v>-0.6754090785980225</v>
+        <v>-8.592954635620117</v>
       </c>
       <c r="M78" t="n">
-        <v>-11.15882301330566</v>
+        <v>-12.96053504943848</v>
       </c>
       <c r="N78" t="n">
-        <v>-12.50483322143555</v>
+        <v>3.854934453964233</v>
       </c>
       <c r="O78" t="n">
-        <v>-8.705537796020508</v>
+        <v>-4.597562789916992</v>
       </c>
       <c r="P78" t="n">
-        <v>-8.155506134033203</v>
+        <v>-8.279567718505859</v>
       </c>
       <c r="Q78" t="n">
-        <v>106.4656829833984</v>
+        <v>97.86956024169922</v>
       </c>
       <c r="R78" t="n">
-        <v>48.88466262817383</v>
+        <v>57.71438980102539</v>
       </c>
       <c r="S78" t="n">
-        <v>35.45600891113281</v>
+        <v>46.75894927978516</v>
       </c>
       <c r="T78" t="n">
-        <v>32.61907577514648</v>
+        <v>32.36280822753906</v>
       </c>
       <c r="U78" t="n">
-        <v>22.51460838317871</v>
+        <v>18.50816535949707</v>
       </c>
       <c r="V78" t="n">
-        <v>20.42388534545898</v>
+        <v>22.63165855407715</v>
       </c>
       <c r="W78" t="n">
-        <v>14.98693084716797</v>
+        <v>18.74880218505859</v>
       </c>
       <c r="X78" t="n">
-        <v>14.11903953552246</v>
+        <v>11.94958877563477</v>
       </c>
       <c r="Y78" t="n">
-        <v>14.4618616104126</v>
+        <v>14.44866466522217</v>
       </c>
       <c r="Z78" t="n">
-        <v>9.938737869262695</v>
+        <v>12.14589977264404</v>
       </c>
       <c r="AA78" t="n">
-        <v>9.666037559509277</v>
+        <v>10.23093128204346</v>
       </c>
       <c r="AB78" t="n">
-        <v>10.90330410003662</v>
+        <v>9.25855827331543</v>
       </c>
       <c r="AC78" t="n">
-        <v>9.622568130493164</v>
+        <v>10.18418788909912</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>person 9</t>
+          <t>person 6</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>vaishnavi_1.ogg</t>
+          <t>Tejender_2.ogg</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>dataset\person 9\vaishnavi_1.ogg</t>
+          <t>dataset\person 6\Tejender_2.ogg</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>-256.3796081542969</v>
+        <v>-279.4379577636719</v>
       </c>
       <c r="E79" t="n">
-        <v>98.49275970458984</v>
+        <v>133.3796234130859</v>
       </c>
       <c r="F79" t="n">
-        <v>8.732111930847168</v>
+        <v>-32.24570465087891</v>
       </c>
       <c r="G79" t="n">
-        <v>30.44884872436523</v>
+        <v>33.45166015625</v>
       </c>
       <c r="H79" t="n">
-        <v>-7.923402309417725</v>
+        <v>20.97794532775879</v>
       </c>
       <c r="I79" t="n">
-        <v>-7.455092430114746</v>
+        <v>1.798129558563232</v>
       </c>
       <c r="J79" t="n">
-        <v>-19.39515495300293</v>
+        <v>-17.07165145874023</v>
       </c>
       <c r="K79" t="n">
-        <v>-19.24704360961914</v>
+        <v>-9.722966194152832</v>
       </c>
       <c r="L79" t="n">
-        <v>-4.155113697052002</v>
+        <v>-7.129319190979004</v>
       </c>
       <c r="M79" t="n">
-        <v>-9.748040199279785</v>
+        <v>-11.12513542175293</v>
       </c>
       <c r="N79" t="n">
-        <v>-8.807007789611816</v>
+        <v>-0.7795337438583374</v>
       </c>
       <c r="O79" t="n">
-        <v>-6.999690055847168</v>
+        <v>-5.830524444580078</v>
       </c>
       <c r="P79" t="n">
-        <v>0.4338657259941101</v>
+        <v>-6.15012264251709</v>
       </c>
       <c r="Q79" t="n">
-        <v>121.5381088256836</v>
+        <v>104.7699127197266</v>
       </c>
       <c r="R79" t="n">
-        <v>39.5520133972168</v>
+        <v>53.32034683227539</v>
       </c>
       <c r="S79" t="n">
-        <v>45.04905700683594</v>
+        <v>52.46269226074219</v>
       </c>
       <c r="T79" t="n">
-        <v>25.2275562286377</v>
+        <v>32.73448944091797</v>
       </c>
       <c r="U79" t="n">
-        <v>26.77007865905762</v>
+        <v>25.35870552062988</v>
       </c>
       <c r="V79" t="n">
-        <v>13.50710296630859</v>
+        <v>22.62563133239746</v>
       </c>
       <c r="W79" t="n">
-        <v>14.61097717285156</v>
+        <v>19.90865898132324</v>
       </c>
       <c r="X79" t="n">
-        <v>15.18807888031006</v>
+        <v>15.17664623260498</v>
       </c>
       <c r="Y79" t="n">
-        <v>13.30795669555664</v>
+        <v>15.14743232727051</v>
       </c>
       <c r="Z79" t="n">
-        <v>11.20494937896729</v>
+        <v>11.42538166046143</v>
       </c>
       <c r="AA79" t="n">
-        <v>10.87530899047852</v>
+        <v>9.400094985961914</v>
       </c>
       <c r="AB79" t="n">
-        <v>11.49388599395752</v>
+        <v>8.645046234130859</v>
       </c>
       <c r="AC79" t="n">
-        <v>8.31267261505127</v>
+        <v>8.31033992767334</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>person 7</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>jheel_1.ogg</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>dataset\person 7\jheel_1.ogg</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>-317.1886596679688</v>
+      </c>
+      <c r="E80" t="n">
+        <v>139.5738220214844</v>
+      </c>
+      <c r="F80" t="n">
+        <v>24.0166072845459</v>
+      </c>
+      <c r="G80" t="n">
+        <v>14.53670024871826</v>
+      </c>
+      <c r="H80" t="n">
+        <v>8.242179870605469</v>
+      </c>
+      <c r="I80" t="n">
+        <v>3.172555685043335</v>
+      </c>
+      <c r="J80" t="n">
+        <v>-21.8743782043457</v>
+      </c>
+      <c r="K80" t="n">
+        <v>2.076800346374512</v>
+      </c>
+      <c r="L80" t="n">
+        <v>-8.145941734313965</v>
+      </c>
+      <c r="M80" t="n">
+        <v>-6.731777191162109</v>
+      </c>
+      <c r="N80" t="n">
+        <v>-7.22862434387207</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1.637333869934082</v>
+      </c>
+      <c r="P80" t="n">
+        <v>5.000531673431396</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>77.30405426025391</v>
+      </c>
+      <c r="R80" t="n">
+        <v>41.21332931518555</v>
+      </c>
+      <c r="S80" t="n">
+        <v>32.35728073120117</v>
+      </c>
+      <c r="T80" t="n">
+        <v>27.92392349243164</v>
+      </c>
+      <c r="U80" t="n">
+        <v>15.14712429046631</v>
+      </c>
+      <c r="V80" t="n">
+        <v>13.10469722747803</v>
+      </c>
+      <c r="W80" t="n">
+        <v>17.39910125732422</v>
+      </c>
+      <c r="X80" t="n">
+        <v>14.41896820068359</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>13.33712196350098</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>8.719347953796387</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>11.32425308227539</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>8.552587509155273</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>9.569530487060547</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>person 7</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>jheel_2.ogg</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>dataset\person 7\jheel_2.ogg</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>-229.3513336181641</v>
+      </c>
+      <c r="E81" t="n">
+        <v>99.31137084960938</v>
+      </c>
+      <c r="F81" t="n">
+        <v>13.41466331481934</v>
+      </c>
+      <c r="G81" t="n">
+        <v>13.3733549118042</v>
+      </c>
+      <c r="H81" t="n">
+        <v>3.016288757324219</v>
+      </c>
+      <c r="I81" t="n">
+        <v>-12.59360885620117</v>
+      </c>
+      <c r="J81" t="n">
+        <v>-13.31148147583008</v>
+      </c>
+      <c r="K81" t="n">
+        <v>-2.699369430541992</v>
+      </c>
+      <c r="L81" t="n">
+        <v>-6.242746353149414</v>
+      </c>
+      <c r="M81" t="n">
+        <v>-9.442974090576172</v>
+      </c>
+      <c r="N81" t="n">
+        <v>1.134596467018127</v>
+      </c>
+      <c r="O81" t="n">
+        <v>-3.44888162612915</v>
+      </c>
+      <c r="P81" t="n">
+        <v>3.6424241065979</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>111.5307312011719</v>
+      </c>
+      <c r="R81" t="n">
+        <v>41.49425506591797</v>
+      </c>
+      <c r="S81" t="n">
+        <v>41.6881103515625</v>
+      </c>
+      <c r="T81" t="n">
+        <v>28.65260314941406</v>
+      </c>
+      <c r="U81" t="n">
+        <v>16.42165946960449</v>
+      </c>
+      <c r="V81" t="n">
+        <v>18.10476875305176</v>
+      </c>
+      <c r="W81" t="n">
+        <v>14.88711261749268</v>
+      </c>
+      <c r="X81" t="n">
+        <v>14.33713817596436</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>13.68465805053711</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>10.41324424743652</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>11.4205846786499</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>12.3576831817627</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>9.243979454040527</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>person 8</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ankita_1.ogg</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>dataset\person 8\ankita_1.ogg</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>-270.2237243652344</v>
+      </c>
+      <c r="E82" t="n">
+        <v>58.96270751953125</v>
+      </c>
+      <c r="F82" t="n">
+        <v>38.67244720458984</v>
+      </c>
+      <c r="G82" t="n">
+        <v>8.070169448852539</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-24.42742538452148</v>
+      </c>
+      <c r="I82" t="n">
+        <v>2.1974196434021</v>
+      </c>
+      <c r="J82" t="n">
+        <v>-7.311805248260498</v>
+      </c>
+      <c r="K82" t="n">
+        <v>-10.53012466430664</v>
+      </c>
+      <c r="L82" t="n">
+        <v>-5.142326354980469</v>
+      </c>
+      <c r="M82" t="n">
+        <v>-2.67604398727417</v>
+      </c>
+      <c r="N82" t="n">
+        <v>-12.98607063293457</v>
+      </c>
+      <c r="O82" t="n">
+        <v>-10.37759876251221</v>
+      </c>
+      <c r="P82" t="n">
+        <v>-8.26213550567627</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>122.35009765625</v>
+      </c>
+      <c r="R82" t="n">
+        <v>53.08518600463867</v>
+      </c>
+      <c r="S82" t="n">
+        <v>39.09588241577148</v>
+      </c>
+      <c r="T82" t="n">
+        <v>27.46438217163086</v>
+      </c>
+      <c r="U82" t="n">
+        <v>28.98434257507324</v>
+      </c>
+      <c r="V82" t="n">
+        <v>15.67507457733154</v>
+      </c>
+      <c r="W82" t="n">
+        <v>14.56611728668213</v>
+      </c>
+      <c r="X82" t="n">
+        <v>14.58829212188721</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>12.29934310913086</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>10.6221866607666</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>10.70013236999512</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>10.061936378479</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>9.220752716064453</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>person 8</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ankita_2.ogg</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>dataset\person 8\ankita_2.ogg</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>-250.0560913085938</v>
+      </c>
+      <c r="E83" t="n">
+        <v>72.12837219238281</v>
+      </c>
+      <c r="F83" t="n">
+        <v>34.50404357910156</v>
+      </c>
+      <c r="G83" t="n">
+        <v>5.64661693572998</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-31.13961982727051</v>
+      </c>
+      <c r="I83" t="n">
+        <v>-1.317376494407654</v>
+      </c>
+      <c r="J83" t="n">
+        <v>-10.20572566986084</v>
+      </c>
+      <c r="K83" t="n">
+        <v>-14.19919300079346</v>
+      </c>
+      <c r="L83" t="n">
+        <v>-4.693023681640625</v>
+      </c>
+      <c r="M83" t="n">
+        <v>-2.679990768432617</v>
+      </c>
+      <c r="N83" t="n">
+        <v>-15.13342761993408</v>
+      </c>
+      <c r="O83" t="n">
+        <v>-7.792290687561035</v>
+      </c>
+      <c r="P83" t="n">
+        <v>-9.90543270111084</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>119.1896743774414</v>
+      </c>
+      <c r="R83" t="n">
+        <v>51.60607147216797</v>
+      </c>
+      <c r="S83" t="n">
+        <v>37.96743011474609</v>
+      </c>
+      <c r="T83" t="n">
+        <v>28.75864028930664</v>
+      </c>
+      <c r="U83" t="n">
+        <v>29.4977855682373</v>
+      </c>
+      <c r="V83" t="n">
+        <v>17.02374649047852</v>
+      </c>
+      <c r="W83" t="n">
+        <v>14.97891616821289</v>
+      </c>
+      <c r="X83" t="n">
+        <v>14.13392162322998</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>12.5789794921875</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>10.51625442504883</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>10.5496711730957</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>9.269749641418457</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>9.096851348876953</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>person 8</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ankita_4.ogg</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>dataset\person 8\ankita_4.ogg</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>-258.3805236816406</v>
+      </c>
+      <c r="E84" t="n">
+        <v>92.83200073242188</v>
+      </c>
+      <c r="F84" t="n">
+        <v>11.39120864868164</v>
+      </c>
+      <c r="G84" t="n">
+        <v>6.207101821899414</v>
+      </c>
+      <c r="H84" t="n">
+        <v>2.089468240737915</v>
+      </c>
+      <c r="I84" t="n">
+        <v>-20.39954376220703</v>
+      </c>
+      <c r="J84" t="n">
+        <v>-11.28644371032715</v>
+      </c>
+      <c r="K84" t="n">
+        <v>-8.85013484954834</v>
+      </c>
+      <c r="L84" t="n">
+        <v>-0.6754090785980225</v>
+      </c>
+      <c r="M84" t="n">
+        <v>-11.15882301330566</v>
+      </c>
+      <c r="N84" t="n">
+        <v>-12.50483322143555</v>
+      </c>
+      <c r="O84" t="n">
+        <v>-8.705537796020508</v>
+      </c>
+      <c r="P84" t="n">
+        <v>-8.155506134033203</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>106.4656829833984</v>
+      </c>
+      <c r="R84" t="n">
+        <v>48.88466262817383</v>
+      </c>
+      <c r="S84" t="n">
+        <v>35.45600891113281</v>
+      </c>
+      <c r="T84" t="n">
+        <v>32.61907577514648</v>
+      </c>
+      <c r="U84" t="n">
+        <v>22.51460838317871</v>
+      </c>
+      <c r="V84" t="n">
+        <v>20.42388534545898</v>
+      </c>
+      <c r="W84" t="n">
+        <v>14.98693084716797</v>
+      </c>
+      <c r="X84" t="n">
+        <v>14.11903953552246</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>14.4618616104126</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>9.938737869262695</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>9.666037559509277</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>10.90330410003662</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>9.622568130493164</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>person 9</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>vaishnavi_1.ogg</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>dataset\person 9\vaishnavi_1.ogg</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>-256.3796081542969</v>
+      </c>
+      <c r="E85" t="n">
+        <v>98.49275970458984</v>
+      </c>
+      <c r="F85" t="n">
+        <v>8.732111930847168</v>
+      </c>
+      <c r="G85" t="n">
+        <v>30.44884872436523</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-7.923402309417725</v>
+      </c>
+      <c r="I85" t="n">
+        <v>-7.455092430114746</v>
+      </c>
+      <c r="J85" t="n">
+        <v>-19.39515495300293</v>
+      </c>
+      <c r="K85" t="n">
+        <v>-19.24704360961914</v>
+      </c>
+      <c r="L85" t="n">
+        <v>-4.155113697052002</v>
+      </c>
+      <c r="M85" t="n">
+        <v>-9.748040199279785</v>
+      </c>
+      <c r="N85" t="n">
+        <v>-8.807007789611816</v>
+      </c>
+      <c r="O85" t="n">
+        <v>-6.999690055847168</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0.4338657259941101</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>121.5381088256836</v>
+      </c>
+      <c r="R85" t="n">
+        <v>39.5520133972168</v>
+      </c>
+      <c r="S85" t="n">
+        <v>45.04905700683594</v>
+      </c>
+      <c r="T85" t="n">
+        <v>25.2275562286377</v>
+      </c>
+      <c r="U85" t="n">
+        <v>26.77007865905762</v>
+      </c>
+      <c r="V85" t="n">
+        <v>13.50710296630859</v>
+      </c>
+      <c r="W85" t="n">
+        <v>14.61097717285156</v>
+      </c>
+      <c r="X85" t="n">
+        <v>15.18807888031006</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>13.30795669555664</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>11.20494937896729</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>10.87530899047852</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>11.49388599395752</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>8.31267261505127</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>person 9</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
         <is>
           <t>vaishnavi_3.ogg</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>dataset\person 9\vaishnavi_3.ogg</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D86" t="n">
         <v>-251.5499725341797</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E86" t="n">
         <v>92.1644287109375</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F86" t="n">
         <v>6.074502944946289</v>
       </c>
-      <c r="G80" t="n">
+      <c r="G86" t="n">
         <v>33.25386810302734</v>
       </c>
-      <c r="H80" t="n">
+      <c r="H86" t="n">
         <v>-8.293931007385254</v>
       </c>
-      <c r="I80" t="n">
+      <c r="I86" t="n">
         <v>-15.41576957702637</v>
       </c>
-      <c r="J80" t="n">
+      <c r="J86" t="n">
         <v>-23.28523445129395</v>
       </c>
-      <c r="K80" t="n">
+      <c r="K86" t="n">
         <v>-15.47053337097168</v>
       </c>
-      <c r="L80" t="n">
+      <c r="L86" t="n">
         <v>-5.091086387634277</v>
       </c>
-      <c r="M80" t="n">
+      <c r="M86" t="n">
         <v>-11.46393871307373</v>
       </c>
-      <c r="N80" t="n">
+      <c r="N86" t="n">
         <v>-7.56251335144043</v>
       </c>
-      <c r="O80" t="n">
+      <c r="O86" t="n">
         <v>-7.744572162628174</v>
       </c>
-      <c r="P80" t="n">
+      <c r="P86" t="n">
         <v>0.3262795209884644</v>
       </c>
-      <c r="Q80" t="n">
+      <c r="Q86" t="n">
         <v>114.1080551147461</v>
       </c>
-      <c r="R80" t="n">
+      <c r="R86" t="n">
         <v>40.90968322753906</v>
       </c>
-      <c r="S80" t="n">
+      <c r="S86" t="n">
         <v>44.52767944335938</v>
       </c>
-      <c r="T80" t="n">
+      <c r="T86" t="n">
         <v>30.35942077636719</v>
       </c>
-      <c r="U80" t="n">
+      <c r="U86" t="n">
         <v>25.61916351318359</v>
       </c>
-      <c r="V80" t="n">
+      <c r="V86" t="n">
         <v>15.83772468566895</v>
       </c>
-      <c r="W80" t="n">
+      <c r="W86" t="n">
         <v>15.28616619110107</v>
       </c>
-      <c r="X80" t="n">
+      <c r="X86" t="n">
         <v>13.24298763275146</v>
       </c>
-      <c r="Y80" t="n">
+      <c r="Y86" t="n">
         <v>13.70436096191406</v>
       </c>
-      <c r="Z80" t="n">
+      <c r="Z86" t="n">
         <v>11.20803642272949</v>
       </c>
-      <c r="AA80" t="n">
+      <c r="AA86" t="n">
         <v>9.892670631408691</v>
       </c>
-      <c r="AB80" t="n">
+      <c r="AB86" t="n">
         <v>11.61030101776123</v>
       </c>
-      <c r="AC80" t="n">
+      <c r="AC86" t="n">
         <v>8.742694854736328</v>
       </c>
     </row>
